--- a/template_impor_pajak.xlsx
+++ b/template_impor_pajak.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\2026-05-tagih-pajak\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8133D753-E326-4A45-8D5A-E750A8082E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="2352" yWindow="960" windowWidth="20232" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="998">
   <si>
     <t>NOPOL</t>
   </si>
@@ -74,9 +79,6 @@
     <t>27/02/2031</t>
   </si>
   <si>
-    <t>08525932222</t>
-  </si>
-  <si>
     <t>P 3110 SE</t>
   </si>
   <si>
@@ -3009,19 +3011,17 @@
   </si>
   <si>
     <t>08192519498</t>
+  </si>
+  <si>
+    <t>085156804754</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -3047,14 +3047,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3344,28 +3353,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L201"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3403,7 +3408,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3437,25 +3442,25 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
       </c>
       <c r="F3">
         <v>2018</v>
@@ -3470,30 +3475,30 @@
         <v>2885100</v>
       </c>
       <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
       </c>
       <c r="F4">
         <v>2009</v>
@@ -3508,30 +3513,30 @@
         <v>5006600</v>
       </c>
       <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
         <v>32</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>33</v>
       </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
       </c>
       <c r="F5">
         <v>2020</v>
@@ -3546,30 +3551,30 @@
         <v>5079600</v>
       </c>
       <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>40</v>
       </c>
-      <c r="L5" t="s">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
       </c>
       <c r="F6">
         <v>2023</v>
@@ -3584,30 +3589,30 @@
         <v>4681200</v>
       </c>
       <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
         <v>47</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>48</v>
       </c>
-      <c r="L6" t="s">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>50</v>
       </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
       <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
         <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
       </c>
       <c r="F7">
         <v>2008</v>
@@ -3622,30 +3627,30 @@
         <v>2928200</v>
       </c>
       <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
         <v>52</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>53</v>
       </c>
-      <c r="L7" t="s">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
         <v>57</v>
-      </c>
-      <c r="E8" t="s">
-        <v>58</v>
       </c>
       <c r="F8">
         <v>2013</v>
@@ -3660,30 +3665,30 @@
         <v>403700</v>
       </c>
       <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
         <v>59</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>60</v>
       </c>
-      <c r="L8" t="s">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
       <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
       </c>
       <c r="F9">
         <v>2010</v>
@@ -3698,30 +3703,30 @@
         <v>3286800</v>
       </c>
       <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
         <v>64</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>65</v>
       </c>
-      <c r="L9" t="s">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
         <v>69</v>
-      </c>
-      <c r="E10" t="s">
-        <v>70</v>
       </c>
       <c r="F10">
         <v>2008</v>
@@ -3736,30 +3741,30 @@
         <v>130100</v>
       </c>
       <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
         <v>71</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>72</v>
       </c>
-      <c r="L10" t="s">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
       <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
       </c>
       <c r="F11">
         <v>2019</v>
@@ -3774,30 +3779,30 @@
         <v>2994600</v>
       </c>
       <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
         <v>76</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>77</v>
       </c>
-      <c r="L11" t="s">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>82</v>
       </c>
       <c r="F12">
         <v>2024</v>
@@ -3812,30 +3817,30 @@
         <v>4347500</v>
       </c>
       <c r="J12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" t="s">
         <v>83</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>84</v>
       </c>
-      <c r="L12" t="s">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>86</v>
       </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
       <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
       </c>
       <c r="F13">
         <v>2019</v>
@@ -3850,30 +3855,30 @@
         <v>2994600</v>
       </c>
       <c r="J13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" t="s">
         <v>88</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>89</v>
       </c>
-      <c r="L13" t="s">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>91</v>
-      </c>
-      <c r="B14" t="s">
-        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>58</v>
       </c>
       <c r="F14">
         <v>2008</v>
@@ -3888,30 +3893,30 @@
         <v>309100</v>
       </c>
       <c r="J14" t="s">
+        <v>92</v>
+      </c>
+      <c r="K14" t="s">
         <v>93</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>94</v>
       </c>
-      <c r="L14" t="s">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>96</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
         <v>97</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>98</v>
       </c>
       <c r="F15">
         <v>2006</v>
@@ -3926,30 +3931,30 @@
         <v>2070000</v>
       </c>
       <c r="J15" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" t="s">
         <v>99</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>100</v>
       </c>
-      <c r="L15" t="s">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>102</v>
       </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
       <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
         <v>22</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
       </c>
       <c r="F16">
         <v>2012</v>
@@ -3964,30 +3969,30 @@
         <v>2227700</v>
       </c>
       <c r="J16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" t="s">
         <v>104</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>105</v>
       </c>
-      <c r="L16" t="s">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>107</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>109</v>
-      </c>
-      <c r="E17" t="s">
-        <v>110</v>
       </c>
       <c r="F17">
         <v>2008</v>
@@ -4002,30 +4007,30 @@
         <v>3660300</v>
       </c>
       <c r="J17" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" t="s">
         <v>111</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>112</v>
       </c>
-      <c r="L17" t="s">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>114</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
         <v>115</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>116</v>
       </c>
       <c r="F18">
         <v>2022</v>
@@ -4040,30 +4045,30 @@
         <v>4229700</v>
       </c>
       <c r="J18" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" t="s">
         <v>117</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>118</v>
       </c>
-      <c r="L18" t="s">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>120</v>
-      </c>
-      <c r="B19" t="s">
-        <v>121</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F19">
         <v>2007</v>
@@ -4078,30 +4083,30 @@
         <v>244400</v>
       </c>
       <c r="J19" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" t="s">
         <v>123</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>124</v>
       </c>
-      <c r="L19" t="s">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>127</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20">
         <v>2010</v>
@@ -4116,30 +4121,30 @@
         <v>155200</v>
       </c>
       <c r="J20" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" t="s">
         <v>129</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>130</v>
       </c>
-      <c r="L20" t="s">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>132</v>
       </c>
-      <c r="B21" t="s">
-        <v>133</v>
-      </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F21">
         <v>2025</v>
@@ -4154,30 +4159,30 @@
         <v>3320000</v>
       </c>
       <c r="J21" t="s">
+        <v>134</v>
+      </c>
+      <c r="K21" t="s">
         <v>135</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>136</v>
       </c>
-      <c r="L21" t="s">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>138</v>
       </c>
-      <c r="B22" t="s">
-        <v>139</v>
-      </c>
       <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
         <v>22</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
       </c>
       <c r="F22">
         <v>2022</v>
@@ -4192,30 +4197,30 @@
         <v>3323300</v>
       </c>
       <c r="J22" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" t="s">
         <v>140</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>141</v>
       </c>
-      <c r="L22" t="s">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>143</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
         <v>144</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>145</v>
       </c>
       <c r="F23">
         <v>2025</v>
@@ -4230,30 +4235,30 @@
         <v>19920000</v>
       </c>
       <c r="J23" t="s">
+        <v>145</v>
+      </c>
+      <c r="K23" t="s">
         <v>146</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>147</v>
       </c>
-      <c r="L23" t="s">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>149</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s">
         <v>150</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" t="s">
-        <v>151</v>
       </c>
       <c r="F24">
         <v>2014</v>
@@ -4268,30 +4273,30 @@
         <v>2113200</v>
       </c>
       <c r="J24" t="s">
+        <v>151</v>
+      </c>
+      <c r="K24" t="s">
         <v>152</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>153</v>
       </c>
-      <c r="L24" t="s">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>155</v>
       </c>
-      <c r="B25" t="s">
-        <v>156</v>
-      </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" t="s">
         <v>109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>110</v>
       </c>
       <c r="F25">
         <v>2018</v>
@@ -4306,30 +4311,30 @@
         <v>5901300</v>
       </c>
       <c r="J25" t="s">
+        <v>156</v>
+      </c>
+      <c r="K25" t="s">
         <v>157</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>158</v>
       </c>
-      <c r="L25" t="s">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>160</v>
       </c>
-      <c r="B26" t="s">
-        <v>161</v>
-      </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F26">
         <v>2010</v>
@@ -4344,30 +4349,30 @@
         <v>2647700</v>
       </c>
       <c r="J26" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" t="s">
         <v>163</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>164</v>
       </c>
-      <c r="L26" t="s">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>166</v>
-      </c>
-      <c r="B27" t="s">
-        <v>167</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
         <v>69</v>
-      </c>
-      <c r="E27" t="s">
-        <v>70</v>
       </c>
       <c r="F27">
         <v>2023</v>
@@ -4382,30 +4387,30 @@
         <v>249700</v>
       </c>
       <c r="J27" t="s">
+        <v>167</v>
+      </c>
+      <c r="K27" t="s">
         <v>168</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>169</v>
       </c>
-      <c r="L27" t="s">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>171</v>
       </c>
-      <c r="B28" t="s">
-        <v>172</v>
-      </c>
       <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
         <v>44</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>45</v>
-      </c>
-      <c r="E28" t="s">
-        <v>46</v>
       </c>
       <c r="F28">
         <v>2007</v>
@@ -4420,30 +4425,30 @@
         <v>2290800</v>
       </c>
       <c r="J28" t="s">
+        <v>172</v>
+      </c>
+      <c r="K28" t="s">
         <v>173</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>174</v>
       </c>
-      <c r="L28" t="s">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>176</v>
-      </c>
-      <c r="B29" t="s">
-        <v>177</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" t="s">
         <v>69</v>
-      </c>
-      <c r="E29" t="s">
-        <v>70</v>
       </c>
       <c r="F29">
         <v>2023</v>
@@ -4458,30 +4463,30 @@
         <v>249700</v>
       </c>
       <c r="J29" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" t="s">
         <v>178</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>179</v>
       </c>
-      <c r="L29" t="s">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>181</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
         <v>182</v>
       </c>
-      <c r="C30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>183</v>
-      </c>
-      <c r="E30" t="s">
-        <v>184</v>
       </c>
       <c r="F30">
         <v>2025</v>
@@ -4496,30 +4501,30 @@
         <v>9296000</v>
       </c>
       <c r="J30" t="s">
+        <v>184</v>
+      </c>
+      <c r="K30" t="s">
         <v>185</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>186</v>
       </c>
-      <c r="L30" t="s">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>188</v>
       </c>
-      <c r="B31" t="s">
-        <v>189</v>
-      </c>
       <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
         <v>44</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>45</v>
-      </c>
-      <c r="E31" t="s">
-        <v>46</v>
       </c>
       <c r="F31">
         <v>2022</v>
@@ -4534,21 +4539,21 @@
         <v>4531800</v>
       </c>
       <c r="J31" t="s">
+        <v>189</v>
+      </c>
+      <c r="K31" t="s">
         <v>190</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>191</v>
       </c>
-      <c r="L31" t="s">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>193</v>
-      </c>
-      <c r="B32" t="s">
-        <v>194</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -4557,7 +4562,7 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32">
         <v>2021</v>
@@ -4572,30 +4577,30 @@
         <v>350600</v>
       </c>
       <c r="J32" t="s">
+        <v>195</v>
+      </c>
+      <c r="K32" t="s">
         <v>196</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>197</v>
       </c>
-      <c r="L32" t="s">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>199</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
         <v>200</v>
       </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>201</v>
-      </c>
-      <c r="E33" t="s">
-        <v>202</v>
       </c>
       <c r="F33">
         <v>2011</v>
@@ -4610,21 +4615,21 @@
         <v>1636800</v>
       </c>
       <c r="J33" t="s">
+        <v>202</v>
+      </c>
+      <c r="K33" t="s">
         <v>203</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>204</v>
       </c>
-      <c r="L33" t="s">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>206</v>
-      </c>
-      <c r="B34" t="s">
-        <v>207</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -4633,7 +4638,7 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F34">
         <v>2023</v>
@@ -4648,30 +4653,30 @@
         <v>327700</v>
       </c>
       <c r="J34" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" t="s">
         <v>209</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>210</v>
       </c>
-      <c r="L34" t="s">
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>212</v>
       </c>
-      <c r="B35" t="s">
-        <v>213</v>
-      </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F35">
         <v>2025</v>
@@ -4686,21 +4691,21 @@
         <v>19920000</v>
       </c>
       <c r="J35" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" t="s">
         <v>214</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>215</v>
       </c>
-      <c r="L35" t="s">
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>217</v>
-      </c>
-      <c r="B36" t="s">
-        <v>218</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -4709,7 +4714,7 @@
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F36">
         <v>2021</v>
@@ -4724,30 +4729,30 @@
         <v>350600</v>
       </c>
       <c r="J36" t="s">
+        <v>218</v>
+      </c>
+      <c r="K36" t="s">
         <v>219</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>220</v>
       </c>
-      <c r="L36" t="s">
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>222</v>
       </c>
-      <c r="B37" t="s">
-        <v>223</v>
-      </c>
       <c r="C37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
         <v>37</v>
-      </c>
-      <c r="D37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" t="s">
-        <v>38</v>
       </c>
       <c r="F37">
         <v>2017</v>
@@ -4762,30 +4767,30 @@
         <v>4541800</v>
       </c>
       <c r="J37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K37" t="s">
         <v>224</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>225</v>
       </c>
-      <c r="L37" t="s">
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>227</v>
       </c>
-      <c r="B38" t="s">
-        <v>228</v>
-      </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" t="s">
         <v>183</v>
-      </c>
-      <c r="E38" t="s">
-        <v>184</v>
       </c>
       <c r="F38">
         <v>2008</v>
@@ -4800,30 +4805,30 @@
         <v>4555000</v>
       </c>
       <c r="J38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K38" t="s">
+        <v>228</v>
+      </c>
+      <c r="L38" t="s">
         <v>229</v>
       </c>
-      <c r="L38" t="s">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>231</v>
       </c>
-      <c r="B39" t="s">
-        <v>232</v>
-      </c>
       <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
         <v>30</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
       </c>
       <c r="F39">
         <v>2020</v>
@@ -4838,30 +4843,30 @@
         <v>8183800</v>
       </c>
       <c r="J39" t="s">
+        <v>232</v>
+      </c>
+      <c r="K39" t="s">
         <v>233</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>234</v>
       </c>
-      <c r="L39" t="s">
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>236</v>
       </c>
-      <c r="B40" t="s">
-        <v>237</v>
-      </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F40">
         <v>2023</v>
@@ -4876,30 +4881,30 @@
         <v>7489900</v>
       </c>
       <c r="J40" t="s">
+        <v>238</v>
+      </c>
+      <c r="K40" t="s">
         <v>239</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>240</v>
       </c>
-      <c r="L40" t="s">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>242</v>
       </c>
-      <c r="B41" t="s">
-        <v>243</v>
-      </c>
       <c r="C41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" t="s">
         <v>37</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="s">
-        <v>38</v>
       </c>
       <c r="F41">
         <v>2011</v>
@@ -4914,30 +4919,30 @@
         <v>3466100</v>
       </c>
       <c r="J41" t="s">
+        <v>243</v>
+      </c>
+      <c r="K41" t="s">
         <v>244</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>245</v>
       </c>
-      <c r="L41" t="s">
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>247</v>
       </c>
-      <c r="B42" t="s">
-        <v>248</v>
-      </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F42">
         <v>2005</v>
@@ -4952,30 +4957,30 @@
         <v>1925600</v>
       </c>
       <c r="J42" t="s">
+        <v>248</v>
+      </c>
+      <c r="K42" t="s">
         <v>249</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>250</v>
       </c>
-      <c r="L42" t="s">
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>252</v>
       </c>
-      <c r="B43" t="s">
-        <v>253</v>
-      </c>
       <c r="C43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
         <v>37</v>
-      </c>
-      <c r="D43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" t="s">
-        <v>38</v>
       </c>
       <c r="F43">
         <v>2009</v>
@@ -4990,30 +4995,30 @@
         <v>3107500</v>
       </c>
       <c r="J43" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" t="s">
         <v>254</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>255</v>
       </c>
-      <c r="L43" t="s">
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>257</v>
       </c>
-      <c r="B44" t="s">
-        <v>258</v>
-      </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" t="s">
         <v>81</v>
-      </c>
-      <c r="E44" t="s">
-        <v>82</v>
       </c>
       <c r="F44">
         <v>2014</v>
@@ -5028,30 +5033,30 @@
         <v>3002900</v>
       </c>
       <c r="J44" t="s">
+        <v>258</v>
+      </c>
+      <c r="K44" t="s">
         <v>259</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>260</v>
       </c>
-      <c r="L44" t="s">
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>262</v>
       </c>
-      <c r="B45" t="s">
-        <v>263</v>
-      </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F45">
         <v>2017</v>
@@ -5066,21 +5071,21 @@
         <v>15139200</v>
       </c>
       <c r="J45" t="s">
+        <v>263</v>
+      </c>
+      <c r="K45" t="s">
         <v>264</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>265</v>
       </c>
-      <c r="L45" t="s">
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>267</v>
-      </c>
-      <c r="B46" t="s">
-        <v>268</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -5089,7 +5094,7 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F46">
         <v>2010</v>
@@ -5104,30 +5109,30 @@
         <v>191700</v>
       </c>
       <c r="J46" t="s">
+        <v>268</v>
+      </c>
+      <c r="K46" t="s">
         <v>269</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L46" t="s">
         <v>270</v>
       </c>
-      <c r="L46" t="s">
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>272</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" t="s">
         <v>273</v>
-      </c>
-      <c r="C47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" t="s">
-        <v>183</v>
-      </c>
-      <c r="E47" t="s">
-        <v>274</v>
       </c>
       <c r="F47">
         <v>2019</v>
@@ -5142,30 +5147,30 @@
         <v>3266900</v>
       </c>
       <c r="J47" t="s">
+        <v>274</v>
+      </c>
+      <c r="K47" t="s">
         <v>275</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>276</v>
       </c>
-      <c r="L47" t="s">
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>278</v>
       </c>
-      <c r="B48" t="s">
-        <v>279</v>
-      </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F48">
         <v>2010</v>
@@ -5180,30 +5185,30 @@
         <v>4382400</v>
       </c>
       <c r="J48" t="s">
+        <v>279</v>
+      </c>
+      <c r="K48" t="s">
         <v>280</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>281</v>
       </c>
-      <c r="L48" t="s">
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>283</v>
       </c>
-      <c r="B49" t="s">
-        <v>284</v>
-      </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F49">
         <v>2023</v>
@@ -5218,30 +5223,30 @@
         <v>2964800</v>
       </c>
       <c r="J49" t="s">
+        <v>284</v>
+      </c>
+      <c r="K49" t="s">
         <v>285</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>286</v>
       </c>
-      <c r="L49" t="s">
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" t="s">
         <v>289</v>
       </c>
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>290</v>
-      </c>
-      <c r="E50" t="s">
-        <v>291</v>
       </c>
       <c r="F50">
         <v>2022</v>
@@ -5256,30 +5261,30 @@
         <v>5102800</v>
       </c>
       <c r="J50" t="s">
+        <v>291</v>
+      </c>
+      <c r="K50" t="s">
         <v>292</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>293</v>
       </c>
-      <c r="L50" t="s">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>295</v>
       </c>
-      <c r="B51" t="s">
-        <v>296</v>
-      </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
         <v>81</v>
-      </c>
-      <c r="E51" t="s">
-        <v>82</v>
       </c>
       <c r="F51">
         <v>2020</v>
@@ -5294,30 +5299,30 @@
         <v>3809700</v>
       </c>
       <c r="J51" t="s">
+        <v>296</v>
+      </c>
+      <c r="K51" t="s">
         <v>297</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>298</v>
       </c>
-      <c r="L51" t="s">
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>300</v>
       </c>
-      <c r="B52" t="s">
-        <v>301</v>
-      </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F52">
         <v>2023</v>
@@ -5332,30 +5337,30 @@
         <v>7489900</v>
       </c>
       <c r="J52" t="s">
+        <v>301</v>
+      </c>
+      <c r="K52" t="s">
         <v>302</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>303</v>
       </c>
-      <c r="L52" t="s">
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>305</v>
       </c>
-      <c r="B53" t="s">
-        <v>306</v>
-      </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" t="s">
         <v>109</v>
-      </c>
-      <c r="E53" t="s">
-        <v>110</v>
       </c>
       <c r="F53">
         <v>2017</v>
@@ -5370,30 +5375,30 @@
         <v>5677200</v>
       </c>
       <c r="J53" t="s">
+        <v>253</v>
+      </c>
+      <c r="K53" t="s">
         <v>254</v>
       </c>
-      <c r="K53" t="s">
-        <v>255</v>
-      </c>
       <c r="L53" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>308</v>
       </c>
-      <c r="B54" t="s">
-        <v>309</v>
-      </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54">
         <v>2009</v>
@@ -5408,30 +5413,30 @@
         <v>1640100</v>
       </c>
       <c r="J54" t="s">
+        <v>309</v>
+      </c>
+      <c r="K54" t="s">
         <v>310</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>311</v>
       </c>
-      <c r="L54" t="s">
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>313</v>
       </c>
-      <c r="B55" t="s">
-        <v>314</v>
-      </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
+        <v>108</v>
+      </c>
+      <c r="E55" t="s">
         <v>109</v>
-      </c>
-      <c r="E55" t="s">
-        <v>110</v>
       </c>
       <c r="F55">
         <v>2022</v>
@@ -5446,30 +5451,30 @@
         <v>6797700</v>
       </c>
       <c r="J55" t="s">
+        <v>314</v>
+      </c>
+      <c r="K55" t="s">
         <v>315</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>316</v>
       </c>
-      <c r="L55" t="s">
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="56" spans="1:12">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>318</v>
       </c>
-      <c r="B56" t="s">
-        <v>319</v>
-      </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
         <v>81</v>
-      </c>
-      <c r="E56" t="s">
-        <v>82</v>
       </c>
       <c r="F56">
         <v>2010</v>
@@ -5484,30 +5489,30 @@
         <v>2465100</v>
       </c>
       <c r="J56" t="s">
+        <v>319</v>
+      </c>
+      <c r="K56" t="s">
         <v>320</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" t="s">
         <v>321</v>
       </c>
-      <c r="L56" t="s">
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>323</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" t="s">
         <v>324</v>
-      </c>
-      <c r="C57" t="s">
-        <v>37</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s">
-        <v>325</v>
       </c>
       <c r="F57">
         <v>2012</v>
@@ -5522,30 +5527,30 @@
         <v>1822700</v>
       </c>
       <c r="J57" t="s">
+        <v>325</v>
+      </c>
+      <c r="K57" t="s">
         <v>326</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>327</v>
       </c>
-      <c r="L57" t="s">
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>329</v>
       </c>
-      <c r="B58" t="s">
-        <v>330</v>
-      </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F58">
         <v>2007</v>
@@ -5560,30 +5565,30 @@
         <v>1374500</v>
       </c>
       <c r="J58" t="s">
+        <v>330</v>
+      </c>
+      <c r="K58" t="s">
         <v>331</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>332</v>
       </c>
-      <c r="L58" t="s">
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>334</v>
       </c>
-      <c r="B59" t="s">
-        <v>335</v>
-      </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
+        <v>182</v>
+      </c>
+      <c r="E59" t="s">
         <v>183</v>
-      </c>
-      <c r="E59" t="s">
-        <v>184</v>
       </c>
       <c r="F59">
         <v>2023</v>
@@ -5598,30 +5603,30 @@
         <v>8738200</v>
       </c>
       <c r="J59" t="s">
+        <v>335</v>
+      </c>
+      <c r="K59" t="s">
         <v>336</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>337</v>
       </c>
-      <c r="L59" t="s">
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>339</v>
       </c>
-      <c r="B60" t="s">
-        <v>340</v>
-      </c>
       <c r="C60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
         <v>109</v>
-      </c>
-      <c r="E60" t="s">
-        <v>110</v>
       </c>
       <c r="F60">
         <v>2021</v>
@@ -5636,21 +5641,21 @@
         <v>6573600</v>
       </c>
       <c r="J60" t="s">
+        <v>340</v>
+      </c>
+      <c r="K60" t="s">
         <v>341</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>342</v>
       </c>
-      <c r="L60" t="s">
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>344</v>
-      </c>
-      <c r="B61" t="s">
-        <v>345</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -5674,30 +5679,30 @@
         <v>209200</v>
       </c>
       <c r="J61" t="s">
+        <v>345</v>
+      </c>
+      <c r="K61" t="s">
         <v>346</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>347</v>
       </c>
-      <c r="L61" t="s">
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>349</v>
       </c>
-      <c r="B62" t="s">
-        <v>350</v>
-      </c>
       <c r="C62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" t="s">
         <v>22</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>23</v>
-      </c>
-      <c r="E62" t="s">
-        <v>24</v>
       </c>
       <c r="F62">
         <v>2012</v>
@@ -5712,30 +5717,30 @@
         <v>2227700</v>
       </c>
       <c r="J62" t="s">
+        <v>350</v>
+      </c>
+      <c r="K62" t="s">
         <v>351</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>352</v>
       </c>
-      <c r="L62" t="s">
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>354</v>
       </c>
-      <c r="B63" t="s">
-        <v>355</v>
-      </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" t="s">
         <v>81</v>
-      </c>
-      <c r="E63" t="s">
-        <v>82</v>
       </c>
       <c r="F63">
         <v>2006</v>
@@ -5750,30 +5755,30 @@
         <v>1927300</v>
       </c>
       <c r="J63" t="s">
+        <v>151</v>
+      </c>
+      <c r="K63" t="s">
         <v>152</v>
       </c>
-      <c r="K63" t="s">
-        <v>153</v>
-      </c>
       <c r="L63" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>357</v>
       </c>
-      <c r="B64" t="s">
-        <v>358</v>
-      </c>
       <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
         <v>30</v>
-      </c>
-      <c r="D64" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
       </c>
       <c r="F64">
         <v>2020</v>
@@ -5788,30 +5793,30 @@
         <v>8183800</v>
       </c>
       <c r="J64" t="s">
+        <v>358</v>
+      </c>
+      <c r="K64" t="s">
         <v>359</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>360</v>
       </c>
-      <c r="L64" t="s">
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>362</v>
       </c>
-      <c r="B65" t="s">
-        <v>363</v>
-      </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F65">
         <v>2017</v>
@@ -5826,30 +5831,30 @@
         <v>15139200</v>
       </c>
       <c r="J65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K65" t="s">
+        <v>363</v>
+      </c>
+      <c r="L65" t="s">
         <v>364</v>
       </c>
-      <c r="L65" t="s">
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>366</v>
       </c>
-      <c r="B66" t="s">
-        <v>367</v>
-      </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
         <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F66">
         <v>2014</v>
@@ -5864,21 +5869,21 @@
         <v>3225400</v>
       </c>
       <c r="J66" t="s">
+        <v>367</v>
+      </c>
+      <c r="K66" t="s">
         <v>368</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>369</v>
       </c>
-      <c r="L66" t="s">
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>371</v>
-      </c>
-      <c r="B67" t="s">
-        <v>372</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -5887,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F67">
         <v>2013</v>
@@ -5902,21 +5907,21 @@
         <v>255000</v>
       </c>
       <c r="J67" t="s">
+        <v>372</v>
+      </c>
+      <c r="K67" t="s">
         <v>373</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>374</v>
       </c>
-      <c r="L67" t="s">
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>376</v>
-      </c>
-      <c r="B68" t="s">
-        <v>377</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -5925,7 +5930,7 @@
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F68">
         <v>2005</v>
@@ -5940,30 +5945,30 @@
         <v>159400</v>
       </c>
       <c r="J68" t="s">
+        <v>377</v>
+      </c>
+      <c r="K68" t="s">
         <v>378</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>379</v>
       </c>
-      <c r="L68" t="s">
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>381</v>
       </c>
-      <c r="B69" t="s">
-        <v>382</v>
-      </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F69">
         <v>2008</v>
@@ -5978,30 +5983,30 @@
         <v>9760800</v>
       </c>
       <c r="J69" t="s">
+        <v>382</v>
+      </c>
+      <c r="K69" t="s">
         <v>383</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>384</v>
       </c>
-      <c r="L69" t="s">
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>386</v>
-      </c>
-      <c r="B70" t="s">
-        <v>387</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F70">
         <v>2009</v>
@@ -6016,30 +6021,30 @@
         <v>146700</v>
       </c>
       <c r="J70" t="s">
+        <v>387</v>
+      </c>
+      <c r="K70" t="s">
         <v>388</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>389</v>
       </c>
-      <c r="L70" t="s">
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>391</v>
       </c>
-      <c r="B71" t="s">
-        <v>392</v>
-      </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
         <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F71">
         <v>2017</v>
@@ -6054,30 +6059,30 @@
         <v>3658600</v>
       </c>
       <c r="J71" t="s">
+        <v>392</v>
+      </c>
+      <c r="K71" t="s">
         <v>393</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>394</v>
       </c>
-      <c r="L71" t="s">
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>396</v>
       </c>
-      <c r="B72" t="s">
-        <v>397</v>
-      </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E72" t="s">
         <v>201</v>
-      </c>
-      <c r="E72" t="s">
-        <v>202</v>
       </c>
       <c r="F72">
         <v>2010</v>
@@ -6092,30 +6097,30 @@
         <v>1552100</v>
       </c>
       <c r="J72" t="s">
+        <v>397</v>
+      </c>
+      <c r="K72" t="s">
         <v>398</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>399</v>
       </c>
-      <c r="L72" t="s">
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>401</v>
       </c>
-      <c r="B73" t="s">
-        <v>402</v>
-      </c>
       <c r="C73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" t="s">
         <v>109</v>
-      </c>
-      <c r="E73" t="s">
-        <v>110</v>
       </c>
       <c r="F73">
         <v>2005</v>
@@ -6130,30 +6135,30 @@
         <v>2988000</v>
       </c>
       <c r="J73" t="s">
+        <v>402</v>
+      </c>
+      <c r="K73" t="s">
         <v>403</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>404</v>
       </c>
-      <c r="L73" t="s">
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>406</v>
       </c>
-      <c r="B74" t="s">
-        <v>407</v>
-      </c>
       <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
         <v>22</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>23</v>
-      </c>
-      <c r="E74" t="s">
-        <v>24</v>
       </c>
       <c r="F74">
         <v>2020</v>
@@ -6168,30 +6173,30 @@
         <v>3104200</v>
       </c>
       <c r="J74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K74" t="s">
+        <v>407</v>
+      </c>
+      <c r="L74" t="s">
         <v>408</v>
       </c>
-      <c r="L74" t="s">
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>410</v>
       </c>
-      <c r="B75" t="s">
-        <v>411</v>
-      </c>
       <c r="C75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E75" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F75">
         <v>2018</v>
@@ -6206,30 +6211,30 @@
         <v>2360500</v>
       </c>
       <c r="J75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K75" t="s">
+        <v>411</v>
+      </c>
+      <c r="L75" t="s">
         <v>412</v>
       </c>
-      <c r="L75" t="s">
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>414</v>
       </c>
-      <c r="B76" t="s">
-        <v>415</v>
-      </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F76">
         <v>2015</v>
@@ -6244,30 +6249,30 @@
         <v>13944000</v>
       </c>
       <c r="J76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K76" t="s">
+        <v>415</v>
+      </c>
+      <c r="L76" t="s">
         <v>416</v>
       </c>
-      <c r="L76" t="s">
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>418</v>
       </c>
-      <c r="B77" t="s">
-        <v>419</v>
-      </c>
       <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
         <v>22</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>23</v>
-      </c>
-      <c r="E77" t="s">
-        <v>24</v>
       </c>
       <c r="F77">
         <v>2013</v>
@@ -6282,30 +6287,30 @@
         <v>2337300</v>
       </c>
       <c r="J77" t="s">
+        <v>419</v>
+      </c>
+      <c r="K77" t="s">
         <v>420</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>421</v>
       </c>
-      <c r="L77" t="s">
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>423</v>
       </c>
-      <c r="B78" t="s">
-        <v>424</v>
-      </c>
       <c r="C78" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" t="s">
         <v>37</v>
-      </c>
-      <c r="D78" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" t="s">
-        <v>38</v>
       </c>
       <c r="F78">
         <v>2017</v>
@@ -6320,30 +6325,30 @@
         <v>4541800</v>
       </c>
       <c r="J78" t="s">
+        <v>424</v>
+      </c>
+      <c r="K78" t="s">
         <v>425</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>426</v>
       </c>
-      <c r="L78" t="s">
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>428</v>
-      </c>
-      <c r="B79" t="s">
-        <v>429</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F79">
         <v>2015</v>
@@ -6358,30 +6363,30 @@
         <v>197500</v>
       </c>
       <c r="J79" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K79" t="s">
+        <v>429</v>
+      </c>
+      <c r="L79" t="s">
         <v>430</v>
       </c>
-      <c r="L79" t="s">
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" t="s">
-        <v>432</v>
-      </c>
       <c r="B80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" t="s">
         <v>69</v>
-      </c>
-      <c r="E80" t="s">
-        <v>70</v>
       </c>
       <c r="F80">
         <v>2013</v>
@@ -6396,30 +6401,30 @@
         <v>170000</v>
       </c>
       <c r="J80" t="s">
+        <v>432</v>
+      </c>
+      <c r="K80" t="s">
         <v>433</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>434</v>
       </c>
-      <c r="L80" t="s">
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>436</v>
-      </c>
-      <c r="B81" t="s">
-        <v>437</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
+        <v>68</v>
+      </c>
+      <c r="E81" t="s">
         <v>69</v>
-      </c>
-      <c r="E81" t="s">
-        <v>70</v>
       </c>
       <c r="F81">
         <v>2017</v>
@@ -6434,30 +6439,30 @@
         <v>201900</v>
       </c>
       <c r="J81" t="s">
+        <v>437</v>
+      </c>
+      <c r="K81" t="s">
         <v>438</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>439</v>
       </c>
-      <c r="L81" t="s">
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>441</v>
       </c>
-      <c r="B82" t="s">
-        <v>442</v>
-      </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" t="s">
         <v>109</v>
-      </c>
-      <c r="E82" t="s">
-        <v>110</v>
       </c>
       <c r="F82">
         <v>2021</v>
@@ -6472,30 +6477,30 @@
         <v>6573600</v>
       </c>
       <c r="J82" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K82" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L82" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>444</v>
       </c>
-      <c r="B83" t="s">
-        <v>445</v>
-      </c>
       <c r="C83" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" t="s">
+        <v>22</v>
+      </c>
+      <c r="E83" t="s">
         <v>30</v>
-      </c>
-      <c r="D83" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" t="s">
-        <v>31</v>
       </c>
       <c r="F83">
         <v>2007</v>
@@ -6510,30 +6515,30 @@
         <v>4428900</v>
       </c>
       <c r="J83" t="s">
+        <v>445</v>
+      </c>
+      <c r="K83" t="s">
         <v>446</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>447</v>
       </c>
-      <c r="L83" t="s">
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>449</v>
       </c>
-      <c r="B84" t="s">
-        <v>450</v>
-      </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D84" t="s">
+        <v>182</v>
+      </c>
+      <c r="E84" t="s">
         <v>183</v>
-      </c>
-      <c r="E84" t="s">
-        <v>184</v>
       </c>
       <c r="F84">
         <v>2014</v>
@@ -6548,30 +6553,30 @@
         <v>6228300</v>
       </c>
       <c r="J84" t="s">
+        <v>450</v>
+      </c>
+      <c r="K84" t="s">
         <v>451</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>452</v>
       </c>
-      <c r="L84" t="s">
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>454</v>
       </c>
-      <c r="B85" t="s">
-        <v>455</v>
-      </c>
       <c r="C85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" t="s">
+        <v>22</v>
+      </c>
+      <c r="E85" t="s">
         <v>37</v>
-      </c>
-      <c r="D85" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" t="s">
-        <v>38</v>
       </c>
       <c r="F85">
         <v>2023</v>
@@ -6586,30 +6591,30 @@
         <v>5617400</v>
       </c>
       <c r="J85" t="s">
+        <v>455</v>
+      </c>
+      <c r="K85" t="s">
         <v>456</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>457</v>
       </c>
-      <c r="L85" t="s">
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>459</v>
       </c>
-      <c r="B86" t="s">
-        <v>460</v>
-      </c>
       <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
         <v>22</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>23</v>
-      </c>
-      <c r="E86" t="s">
-        <v>24</v>
       </c>
       <c r="F86">
         <v>2024</v>
@@ -6624,30 +6629,30 @@
         <v>3542400</v>
       </c>
       <c r="J86" t="s">
+        <v>460</v>
+      </c>
+      <c r="K86" t="s">
         <v>461</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>462</v>
       </c>
-      <c r="L86" t="s">
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>464</v>
-      </c>
-      <c r="B87" t="s">
-        <v>465</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
+        <v>68</v>
+      </c>
+      <c r="E87" t="s">
         <v>69</v>
-      </c>
-      <c r="E87" t="s">
-        <v>70</v>
       </c>
       <c r="F87">
         <v>2025</v>
@@ -6662,21 +6667,21 @@
         <v>265600</v>
       </c>
       <c r="J87" t="s">
+        <v>465</v>
+      </c>
+      <c r="K87" t="s">
         <v>466</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>467</v>
       </c>
-      <c r="L87" t="s">
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>469</v>
-      </c>
-      <c r="B88" t="s">
-        <v>470</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6703,18 +6708,18 @@
         <v>17</v>
       </c>
       <c r="K88" t="s">
+        <v>470</v>
+      </c>
+      <c r="L88" t="s">
         <v>471</v>
       </c>
-      <c r="L88" t="s">
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>473</v>
-      </c>
-      <c r="B89" t="s">
-        <v>474</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6738,30 +6743,30 @@
         <v>191200</v>
       </c>
       <c r="J89" t="s">
+        <v>474</v>
+      </c>
+      <c r="K89" t="s">
         <v>475</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>476</v>
       </c>
-      <c r="L89" t="s">
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="90" spans="1:12">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>478</v>
       </c>
-      <c r="B90" t="s">
-        <v>479</v>
-      </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F90">
         <v>2018</v>
@@ -6776,30 +6781,30 @@
         <v>15736800</v>
       </c>
       <c r="J90" t="s">
+        <v>479</v>
+      </c>
+      <c r="K90" t="s">
         <v>480</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" t="s">
         <v>481</v>
       </c>
-      <c r="L90" t="s">
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>483</v>
-      </c>
-      <c r="B91" t="s">
-        <v>484</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F91">
         <v>2018</v>
@@ -6814,30 +6819,30 @@
         <v>222900</v>
       </c>
       <c r="J91" t="s">
+        <v>484</v>
+      </c>
+      <c r="K91" t="s">
         <v>485</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" t="s">
         <v>486</v>
       </c>
-      <c r="L91" t="s">
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="92" spans="1:12">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>488</v>
       </c>
-      <c r="B92" t="s">
-        <v>489</v>
-      </c>
       <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" t="s">
         <v>37</v>
-      </c>
-      <c r="D92" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" t="s">
-        <v>38</v>
       </c>
       <c r="F92">
         <v>2010</v>
@@ -6852,30 +6857,30 @@
         <v>3286800</v>
       </c>
       <c r="J92" t="s">
+        <v>489</v>
+      </c>
+      <c r="K92" t="s">
+        <v>135</v>
+      </c>
+      <c r="L92" t="s">
         <v>490</v>
       </c>
-      <c r="K92" t="s">
-        <v>136</v>
-      </c>
-      <c r="L92" t="s">
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="A93" t="s">
+      <c r="B93" t="s">
         <v>492</v>
       </c>
-      <c r="B93" t="s">
-        <v>493</v>
-      </c>
       <c r="C93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
+        <v>200</v>
+      </c>
+      <c r="E93" t="s">
         <v>201</v>
-      </c>
-      <c r="E93" t="s">
-        <v>202</v>
       </c>
       <c r="F93">
         <v>2017</v>
@@ -6890,30 +6895,30 @@
         <v>2144700</v>
       </c>
       <c r="J93" t="s">
+        <v>493</v>
+      </c>
+      <c r="K93" t="s">
         <v>494</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" t="s">
         <v>495</v>
       </c>
-      <c r="L93" t="s">
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="A94" t="s">
+      <c r="B94" t="s">
         <v>497</v>
       </c>
-      <c r="B94" t="s">
-        <v>498</v>
-      </c>
       <c r="C94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F94">
         <v>2011</v>
@@ -6928,30 +6933,30 @@
         <v>2310700</v>
       </c>
       <c r="J94" t="s">
+        <v>498</v>
+      </c>
+      <c r="K94" t="s">
         <v>499</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>500</v>
       </c>
-      <c r="L94" t="s">
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="95" spans="1:12">
-      <c r="A95" t="s">
+      <c r="B95" t="s">
         <v>502</v>
-      </c>
-      <c r="B95" t="s">
-        <v>503</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E95" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F95">
         <v>2009</v>
@@ -6966,30 +6971,30 @@
         <v>276200</v>
       </c>
       <c r="J95" t="s">
+        <v>503</v>
+      </c>
+      <c r="K95" t="s">
         <v>504</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>505</v>
       </c>
-      <c r="L95" t="s">
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="96" spans="1:12">
-      <c r="A96" t="s">
+      <c r="B96" t="s">
         <v>507</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" t="s">
+        <v>182</v>
+      </c>
+      <c r="E96" t="s">
         <v>508</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" t="s">
-        <v>183</v>
-      </c>
-      <c r="E96" t="s">
-        <v>509</v>
       </c>
       <c r="F96">
         <v>2010</v>
@@ -7004,30 +7009,30 @@
         <v>2556400</v>
       </c>
       <c r="J96" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K96" t="s">
+        <v>509</v>
+      </c>
+      <c r="L96" t="s">
         <v>510</v>
       </c>
-      <c r="L96" t="s">
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
         <v>512</v>
       </c>
-      <c r="B97" t="s">
-        <v>513</v>
-      </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F97">
         <v>2022</v>
@@ -7042,30 +7047,30 @@
         <v>7250900</v>
       </c>
       <c r="J97" t="s">
+        <v>513</v>
+      </c>
+      <c r="K97" t="s">
         <v>514</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
         <v>515</v>
       </c>
-      <c r="L97" t="s">
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" t="s">
+      <c r="B98" t="s">
         <v>517</v>
-      </c>
-      <c r="B98" t="s">
-        <v>518</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
+        <v>68</v>
+      </c>
+      <c r="E98" t="s">
         <v>69</v>
-      </c>
-      <c r="E98" t="s">
-        <v>70</v>
       </c>
       <c r="F98">
         <v>2022</v>
@@ -7080,30 +7085,30 @@
         <v>241700</v>
       </c>
       <c r="J98" t="s">
+        <v>518</v>
+      </c>
+      <c r="K98" t="s">
         <v>519</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" t="s">
         <v>520</v>
       </c>
-      <c r="L98" t="s">
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
         <v>522</v>
       </c>
-      <c r="B99" t="s">
-        <v>523</v>
-      </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F99">
         <v>2005</v>
@@ -7118,30 +7123,30 @@
         <v>1925600</v>
       </c>
       <c r="J99" t="s">
+        <v>523</v>
+      </c>
+      <c r="K99" t="s">
         <v>524</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>525</v>
       </c>
-      <c r="L99" t="s">
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>527</v>
       </c>
-      <c r="B100" t="s">
-        <v>528</v>
-      </c>
       <c r="C100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100" t="s">
         <v>109</v>
-      </c>
-      <c r="E100" t="s">
-        <v>110</v>
       </c>
       <c r="F100">
         <v>2014</v>
@@ -7156,30 +7161,30 @@
         <v>5004900</v>
       </c>
       <c r="J100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K100" t="s">
+        <v>528</v>
+      </c>
+      <c r="L100" t="s">
         <v>529</v>
       </c>
-      <c r="L100" t="s">
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>531</v>
       </c>
-      <c r="B101" t="s">
-        <v>532</v>
-      </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F101">
         <v>2020</v>
@@ -7194,30 +7199,30 @@
         <v>16932000</v>
       </c>
       <c r="J101" t="s">
+        <v>532</v>
+      </c>
+      <c r="K101" t="s">
         <v>533</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>534</v>
       </c>
-      <c r="L101" t="s">
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>536</v>
       </c>
-      <c r="B102" t="s">
-        <v>537</v>
-      </c>
       <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" t="s">
+        <v>22</v>
+      </c>
+      <c r="E102" t="s">
         <v>37</v>
-      </c>
-      <c r="D102" t="s">
-        <v>23</v>
-      </c>
-      <c r="E102" t="s">
-        <v>38</v>
       </c>
       <c r="F102">
         <v>2015</v>
@@ -7232,30 +7237,30 @@
         <v>4183200</v>
       </c>
       <c r="J102" t="s">
+        <v>537</v>
+      </c>
+      <c r="K102" t="s">
         <v>538</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>539</v>
       </c>
-      <c r="L102" t="s">
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>541</v>
       </c>
-      <c r="B103" t="s">
-        <v>542</v>
-      </c>
       <c r="C103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F103">
         <v>2008</v>
@@ -7270,30 +7275,30 @@
         <v>3904300</v>
       </c>
       <c r="J103" t="s">
+        <v>542</v>
+      </c>
+      <c r="K103" t="s">
         <v>543</v>
       </c>
-      <c r="K103" t="s">
+      <c r="L103" t="s">
         <v>544</v>
       </c>
-      <c r="L103" t="s">
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" t="s">
+      <c r="B104" t="s">
         <v>546</v>
       </c>
-      <c r="B104" t="s">
-        <v>547</v>
-      </c>
       <c r="C104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F104">
         <v>2012</v>
@@ -7308,30 +7313,30 @@
         <v>1822700</v>
       </c>
       <c r="J104" t="s">
+        <v>547</v>
+      </c>
+      <c r="K104" t="s">
         <v>548</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>549</v>
       </c>
-      <c r="L104" t="s">
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="105" spans="1:12">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
         <v>551</v>
       </c>
-      <c r="B105" t="s">
-        <v>552</v>
-      </c>
       <c r="C105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D105" t="s">
+        <v>108</v>
+      </c>
+      <c r="E105" t="s">
         <v>109</v>
-      </c>
-      <c r="E105" t="s">
-        <v>110</v>
       </c>
       <c r="F105">
         <v>2018</v>
@@ -7346,21 +7351,21 @@
         <v>5901300</v>
       </c>
       <c r="J105" t="s">
+        <v>552</v>
+      </c>
+      <c r="K105" t="s">
         <v>553</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>554</v>
       </c>
-      <c r="L105" t="s">
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="106" spans="1:12">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
         <v>556</v>
-      </c>
-      <c r="B106" t="s">
-        <v>557</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -7384,30 +7389,30 @@
         <v>155400</v>
       </c>
       <c r="J106" t="s">
+        <v>557</v>
+      </c>
+      <c r="K106" t="s">
         <v>558</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>559</v>
       </c>
-      <c r="L106" t="s">
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="107" spans="1:12">
-      <c r="A107" t="s">
-        <v>561</v>
-      </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F107">
         <v>2013</v>
@@ -7422,30 +7427,30 @@
         <v>3081000</v>
       </c>
       <c r="J107" t="s">
+        <v>561</v>
+      </c>
+      <c r="K107" t="s">
         <v>562</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" t="s">
         <v>563</v>
       </c>
-      <c r="L107" t="s">
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="108" spans="1:12">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>565</v>
       </c>
-      <c r="B108" t="s">
-        <v>566</v>
-      </c>
       <c r="C108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
+        <v>108</v>
+      </c>
+      <c r="E108" t="s">
         <v>109</v>
-      </c>
-      <c r="E108" t="s">
-        <v>110</v>
       </c>
       <c r="F108">
         <v>2006</v>
@@ -7460,30 +7465,30 @@
         <v>3212100</v>
       </c>
       <c r="J108" t="s">
+        <v>566</v>
+      </c>
+      <c r="K108" t="s">
         <v>567</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" t="s">
         <v>568</v>
       </c>
-      <c r="L108" t="s">
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="109" spans="1:12">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
         <v>570</v>
       </c>
-      <c r="B109" t="s">
-        <v>571</v>
-      </c>
       <c r="C109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F109">
         <v>2018</v>
@@ -7498,30 +7503,30 @@
         <v>2360500</v>
       </c>
       <c r="J109" t="s">
+        <v>571</v>
+      </c>
+      <c r="K109" t="s">
         <v>572</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>573</v>
       </c>
-      <c r="L109" t="s">
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="110" spans="1:12">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>575</v>
       </c>
-      <c r="B110" t="s">
-        <v>576</v>
-      </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D110" t="s">
+        <v>182</v>
+      </c>
+      <c r="E110" t="s">
         <v>183</v>
-      </c>
-      <c r="E110" t="s">
-        <v>184</v>
       </c>
       <c r="F110">
         <v>2006</v>
@@ -7536,30 +7541,30 @@
         <v>3997300</v>
       </c>
       <c r="J110" t="s">
+        <v>184</v>
+      </c>
+      <c r="K110" t="s">
         <v>185</v>
       </c>
-      <c r="K110" t="s">
-        <v>186</v>
-      </c>
       <c r="L110" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="111" spans="1:12">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
         <v>578</v>
       </c>
-      <c r="B111" t="s">
-        <v>579</v>
-      </c>
       <c r="C111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E111" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F111">
         <v>2018</v>
@@ -7574,30 +7579,30 @@
         <v>3671900</v>
       </c>
       <c r="J111" t="s">
+        <v>579</v>
+      </c>
+      <c r="K111" t="s">
         <v>580</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>581</v>
       </c>
-      <c r="L111" t="s">
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="112" spans="1:12">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>583</v>
       </c>
-      <c r="B112" t="s">
-        <v>584</v>
-      </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D112" t="s">
+        <v>108</v>
+      </c>
+      <c r="E112" t="s">
         <v>109</v>
-      </c>
-      <c r="E112" t="s">
-        <v>110</v>
       </c>
       <c r="F112">
         <v>2016</v>
@@ -7612,30 +7617,30 @@
         <v>5453100</v>
       </c>
       <c r="J112" t="s">
+        <v>584</v>
+      </c>
+      <c r="K112" t="s">
         <v>585</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" t="s">
         <v>586</v>
       </c>
-      <c r="L112" t="s">
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="113" spans="1:12">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>588</v>
       </c>
-      <c r="B113" t="s">
-        <v>589</v>
-      </c>
       <c r="C113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E113" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F113">
         <v>2007</v>
@@ -7650,21 +7655,21 @@
         <v>2214400</v>
       </c>
       <c r="J113" t="s">
+        <v>589</v>
+      </c>
+      <c r="K113" t="s">
         <v>590</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>591</v>
       </c>
-      <c r="L113" t="s">
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
         <v>593</v>
-      </c>
-      <c r="B114" t="s">
-        <v>594</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -7673,7 +7678,7 @@
         <v>15</v>
       </c>
       <c r="E114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F114">
         <v>2016</v>
@@ -7688,21 +7693,21 @@
         <v>290800</v>
       </c>
       <c r="J114" t="s">
+        <v>594</v>
+      </c>
+      <c r="K114" t="s">
         <v>595</v>
       </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>596</v>
       </c>
-      <c r="L114" t="s">
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="115" spans="1:12">
-      <c r="A115" t="s">
-        <v>598</v>
-      </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -7726,30 +7731,30 @@
         <v>146400</v>
       </c>
       <c r="J115" t="s">
+        <v>598</v>
+      </c>
+      <c r="K115" t="s">
         <v>599</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>600</v>
       </c>
-      <c r="L115" t="s">
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="116" spans="1:12">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>602</v>
       </c>
-      <c r="B116" t="s">
-        <v>603</v>
-      </c>
       <c r="C116" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F116">
         <v>2006</v>
@@ -7764,30 +7769,30 @@
         <v>3426200</v>
       </c>
       <c r="J116" t="s">
+        <v>603</v>
+      </c>
+      <c r="K116" t="s">
         <v>604</v>
       </c>
-      <c r="K116" t="s">
+      <c r="L116" t="s">
         <v>605</v>
       </c>
-      <c r="L116" t="s">
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="117" spans="1:12">
-      <c r="A117" t="s">
+      <c r="B117" t="s">
         <v>607</v>
       </c>
-      <c r="B117" t="s">
-        <v>608</v>
-      </c>
       <c r="C117" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D117" t="s">
+        <v>289</v>
+      </c>
+      <c r="E117" t="s">
         <v>290</v>
-      </c>
-      <c r="E117" t="s">
-        <v>291</v>
       </c>
       <c r="F117">
         <v>2007</v>
@@ -7802,30 +7807,30 @@
         <v>2579500</v>
       </c>
       <c r="J117" t="s">
+        <v>608</v>
+      </c>
+      <c r="K117" t="s">
         <v>609</v>
       </c>
-      <c r="K117" t="s">
+      <c r="L117" t="s">
         <v>610</v>
       </c>
-      <c r="L117" t="s">
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="118" spans="1:12">
-      <c r="A118" t="s">
-        <v>612</v>
-      </c>
       <c r="B118" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D118" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E118" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F118">
         <v>2013</v>
@@ -7840,30 +7845,30 @@
         <v>2974700</v>
       </c>
       <c r="J118" t="s">
+        <v>612</v>
+      </c>
+      <c r="K118" t="s">
         <v>613</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>614</v>
       </c>
-      <c r="L118" t="s">
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="119" spans="1:12">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>616</v>
       </c>
-      <c r="B119" t="s">
-        <v>617</v>
-      </c>
       <c r="C119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s">
+        <v>200</v>
+      </c>
+      <c r="E119" t="s">
         <v>201</v>
-      </c>
-      <c r="E119" t="s">
-        <v>202</v>
       </c>
       <c r="F119">
         <v>2016</v>
@@ -7878,30 +7883,30 @@
         <v>2060100</v>
       </c>
       <c r="J119" t="s">
+        <v>617</v>
+      </c>
+      <c r="K119" t="s">
         <v>618</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" t="s">
         <v>619</v>
       </c>
-      <c r="L119" t="s">
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="120" spans="1:12">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>621</v>
       </c>
-      <c r="B120" t="s">
-        <v>622</v>
-      </c>
       <c r="C120" t="s">
+        <v>29</v>
+      </c>
+      <c r="D120" t="s">
+        <v>22</v>
+      </c>
+      <c r="E120" t="s">
         <v>30</v>
-      </c>
-      <c r="D120" t="s">
-        <v>23</v>
-      </c>
-      <c r="E120" t="s">
-        <v>31</v>
       </c>
       <c r="F120">
         <v>2005</v>
@@ -7916,30 +7921,30 @@
         <v>3851200</v>
       </c>
       <c r="J120" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K120" t="s">
+        <v>622</v>
+      </c>
+      <c r="L120" t="s">
         <v>623</v>
       </c>
-      <c r="L120" t="s">
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="121" spans="1:12">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>625</v>
       </c>
-      <c r="B121" t="s">
-        <v>626</v>
-      </c>
       <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
         <v>22</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>23</v>
-      </c>
-      <c r="E121" t="s">
-        <v>24</v>
       </c>
       <c r="F121">
         <v>2008</v>
@@ -7954,21 +7959,21 @@
         <v>1789500</v>
       </c>
       <c r="J121" t="s">
+        <v>626</v>
+      </c>
+      <c r="K121" t="s">
+        <v>233</v>
+      </c>
+      <c r="L121" t="s">
         <v>627</v>
       </c>
-      <c r="K121" t="s">
-        <v>234</v>
-      </c>
-      <c r="L121" t="s">
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="122" spans="1:12">
-      <c r="A122" t="s">
+      <c r="B122" t="s">
         <v>629</v>
-      </c>
-      <c r="B122" t="s">
-        <v>630</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -7977,7 +7982,7 @@
         <v>15</v>
       </c>
       <c r="E122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F122">
         <v>2020</v>
@@ -7992,30 +7997,30 @@
         <v>296300</v>
       </c>
       <c r="J122" t="s">
+        <v>630</v>
+      </c>
+      <c r="K122" t="s">
         <v>631</v>
       </c>
-      <c r="K122" t="s">
+      <c r="L122" t="s">
         <v>632</v>
       </c>
-      <c r="L122" t="s">
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="123" spans="1:12">
-      <c r="A123" t="s">
-        <v>634</v>
-      </c>
       <c r="B123" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C123" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
         <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F123">
         <v>2006</v>
@@ -8030,30 +8035,30 @@
         <v>2070000</v>
       </c>
       <c r="J123" t="s">
+        <v>634</v>
+      </c>
+      <c r="K123" t="s">
         <v>635</v>
       </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>636</v>
       </c>
-      <c r="L123" t="s">
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="124" spans="1:12">
-      <c r="A124" t="s">
+      <c r="B124" t="s">
         <v>638</v>
       </c>
-      <c r="B124" t="s">
-        <v>639</v>
-      </c>
       <c r="C124" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" t="s">
         <v>22</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>23</v>
-      </c>
-      <c r="E124" t="s">
-        <v>24</v>
       </c>
       <c r="F124">
         <v>2023</v>
@@ -8068,30 +8073,30 @@
         <v>3432900</v>
       </c>
       <c r="J124" t="s">
+        <v>639</v>
+      </c>
+      <c r="K124" t="s">
         <v>640</v>
       </c>
-      <c r="K124" t="s">
+      <c r="L124" t="s">
         <v>641</v>
       </c>
-      <c r="L124" t="s">
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="125" spans="1:12">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>643</v>
       </c>
-      <c r="B125" t="s">
-        <v>644</v>
-      </c>
       <c r="C125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" t="s">
         <v>44</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>45</v>
-      </c>
-      <c r="E125" t="s">
-        <v>46</v>
       </c>
       <c r="F125">
         <v>2012</v>
@@ -8106,30 +8111,30 @@
         <v>3037800</v>
       </c>
       <c r="J125" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L125" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="126" spans="1:12">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>646</v>
       </c>
-      <c r="B126" t="s">
-        <v>647</v>
-      </c>
       <c r="C126" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s">
         <v>15</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F126">
         <v>2015</v>
@@ -8144,30 +8149,30 @@
         <v>2324000</v>
       </c>
       <c r="J126" t="s">
+        <v>647</v>
+      </c>
+      <c r="K126" t="s">
         <v>648</v>
       </c>
-      <c r="K126" t="s">
+      <c r="L126" t="s">
         <v>649</v>
       </c>
-      <c r="L126" t="s">
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="127" spans="1:12">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>651</v>
       </c>
-      <c r="B127" t="s">
-        <v>652</v>
-      </c>
       <c r="C127" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D127" t="s">
         <v>15</v>
       </c>
       <c r="E127" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F127">
         <v>2023</v>
@@ -8182,30 +8187,30 @@
         <v>7489900</v>
       </c>
       <c r="J127" t="s">
+        <v>652</v>
+      </c>
+      <c r="K127" t="s">
         <v>653</v>
       </c>
-      <c r="K127" t="s">
+      <c r="L127" t="s">
         <v>654</v>
       </c>
-      <c r="L127" t="s">
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="128" spans="1:12">
-      <c r="A128" t="s">
+      <c r="B128" t="s">
         <v>656</v>
       </c>
-      <c r="B128" t="s">
-        <v>657</v>
-      </c>
       <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
         <v>22</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>23</v>
-      </c>
-      <c r="E128" t="s">
-        <v>24</v>
       </c>
       <c r="F128">
         <v>2013</v>
@@ -8220,30 +8225,30 @@
         <v>2337300</v>
       </c>
       <c r="J128" t="s">
+        <v>657</v>
+      </c>
+      <c r="K128" t="s">
         <v>658</v>
       </c>
-      <c r="K128" t="s">
+      <c r="L128" t="s">
         <v>659</v>
       </c>
-      <c r="L128" t="s">
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="129" spans="1:12">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>661</v>
-      </c>
-      <c r="B129" t="s">
-        <v>662</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E129" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F129">
         <v>2014</v>
@@ -8258,30 +8263,30 @@
         <v>189100</v>
       </c>
       <c r="J129" t="s">
+        <v>662</v>
+      </c>
+      <c r="K129" t="s">
         <v>663</v>
       </c>
-      <c r="K129" t="s">
+      <c r="L129" t="s">
         <v>664</v>
       </c>
-      <c r="L129" t="s">
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="130" spans="1:12">
-      <c r="A130" t="s">
+      <c r="B130" t="s">
         <v>666</v>
       </c>
-      <c r="B130" t="s">
-        <v>667</v>
-      </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D130" t="s">
+        <v>182</v>
+      </c>
+      <c r="E130" t="s">
         <v>183</v>
-      </c>
-      <c r="E130" t="s">
-        <v>184</v>
       </c>
       <c r="F130">
         <v>2020</v>
@@ -8296,30 +8301,30 @@
         <v>7901600</v>
       </c>
       <c r="J130" t="s">
+        <v>667</v>
+      </c>
+      <c r="K130" t="s">
         <v>668</v>
       </c>
-      <c r="K130" t="s">
+      <c r="L130" t="s">
         <v>669</v>
       </c>
-      <c r="L130" t="s">
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="131" spans="1:12">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>671</v>
       </c>
-      <c r="B131" t="s">
-        <v>672</v>
-      </c>
       <c r="C131" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" t="s">
         <v>22</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>23</v>
-      </c>
-      <c r="E131" t="s">
-        <v>24</v>
       </c>
       <c r="F131">
         <v>2009</v>
@@ -8334,30 +8339,30 @@
         <v>1899000</v>
       </c>
       <c r="J131" t="s">
+        <v>672</v>
+      </c>
+      <c r="K131" t="s">
         <v>673</v>
       </c>
-      <c r="K131" t="s">
+      <c r="L131" t="s">
         <v>674</v>
       </c>
-      <c r="L131" t="s">
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="132" spans="1:12">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>676</v>
       </c>
-      <c r="B132" t="s">
-        <v>677</v>
-      </c>
       <c r="C132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F132">
         <v>2019</v>
@@ -8372,21 +8377,21 @@
         <v>3266900</v>
       </c>
       <c r="J132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K132" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L132" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="133" spans="1:12">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>679</v>
-      </c>
-      <c r="B133" t="s">
-        <v>680</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -8410,30 +8415,30 @@
         <v>128500</v>
       </c>
       <c r="J133" t="s">
+        <v>680</v>
+      </c>
+      <c r="K133" t="s">
         <v>681</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" t="s">
         <v>682</v>
       </c>
-      <c r="L133" t="s">
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="134" spans="1:12">
-      <c r="A134" t="s">
+      <c r="B134" t="s">
         <v>684</v>
       </c>
-      <c r="B134" t="s">
-        <v>685</v>
-      </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D134" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F134">
         <v>2020</v>
@@ -8448,30 +8453,30 @@
         <v>3950800</v>
       </c>
       <c r="J134" t="s">
+        <v>685</v>
+      </c>
+      <c r="K134" t="s">
         <v>686</v>
       </c>
-      <c r="K134" t="s">
+      <c r="L134" t="s">
         <v>687</v>
       </c>
-      <c r="L134" t="s">
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="135" spans="1:12">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>689</v>
       </c>
-      <c r="B135" t="s">
-        <v>690</v>
-      </c>
       <c r="C135" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" t="s">
         <v>44</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>45</v>
-      </c>
-      <c r="E135" t="s">
-        <v>46</v>
       </c>
       <c r="F135">
         <v>2015</v>
@@ -8486,30 +8491,30 @@
         <v>3486000</v>
       </c>
       <c r="J135" t="s">
+        <v>690</v>
+      </c>
+      <c r="K135" t="s">
         <v>691</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" t="s">
         <v>692</v>
       </c>
-      <c r="L135" t="s">
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="136" spans="1:12">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>694</v>
       </c>
-      <c r="B136" t="s">
-        <v>695</v>
-      </c>
       <c r="C136" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D136" t="s">
+        <v>289</v>
+      </c>
+      <c r="E136" t="s">
         <v>290</v>
-      </c>
-      <c r="E136" t="s">
-        <v>291</v>
       </c>
       <c r="F136">
         <v>2018</v>
@@ -8524,30 +8529,30 @@
         <v>4429900</v>
       </c>
       <c r="J136" t="s">
+        <v>695</v>
+      </c>
+      <c r="K136" t="s">
         <v>696</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" t="s">
         <v>697</v>
       </c>
-      <c r="L136" t="s">
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="137" spans="1:12">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>699</v>
-      </c>
-      <c r="B137" t="s">
-        <v>700</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
+        <v>56</v>
+      </c>
+      <c r="E137" t="s">
         <v>57</v>
-      </c>
-      <c r="E137" t="s">
-        <v>58</v>
       </c>
       <c r="F137">
         <v>2009</v>
@@ -8562,30 +8567,30 @@
         <v>328000</v>
       </c>
       <c r="J137" t="s">
+        <v>700</v>
+      </c>
+      <c r="K137" t="s">
         <v>701</v>
       </c>
-      <c r="K137" t="s">
+      <c r="L137" t="s">
         <v>702</v>
       </c>
-      <c r="L137" t="s">
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="138" spans="1:12">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>704</v>
       </c>
-      <c r="B138" t="s">
-        <v>705</v>
-      </c>
       <c r="C138" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D138" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" t="s">
         <v>290</v>
-      </c>
-      <c r="E138" t="s">
-        <v>291</v>
       </c>
       <c r="F138">
         <v>2018</v>
@@ -8600,30 +8605,30 @@
         <v>4429900</v>
       </c>
       <c r="J138" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L138" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="139" spans="1:12">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
         <v>707</v>
       </c>
-      <c r="B139" t="s">
-        <v>708</v>
-      </c>
       <c r="C139" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D139" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139" t="s">
         <v>183</v>
-      </c>
-      <c r="E139" t="s">
-        <v>184</v>
       </c>
       <c r="F139">
         <v>2012</v>
@@ -8638,30 +8643,30 @@
         <v>5670600</v>
       </c>
       <c r="J139" t="s">
+        <v>708</v>
+      </c>
+      <c r="K139" t="s">
         <v>709</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" t="s">
         <v>710</v>
       </c>
-      <c r="L139" t="s">
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="140" spans="1:12">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
         <v>712</v>
       </c>
-      <c r="B140" t="s">
-        <v>713</v>
-      </c>
       <c r="C140" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D140" t="s">
+        <v>289</v>
+      </c>
+      <c r="E140" t="s">
         <v>290</v>
-      </c>
-      <c r="E140" t="s">
-        <v>291</v>
       </c>
       <c r="F140">
         <v>2024</v>
@@ -8676,30 +8681,30 @@
         <v>5439300</v>
       </c>
       <c r="J140" t="s">
+        <v>713</v>
+      </c>
+      <c r="K140" t="s">
         <v>714</v>
       </c>
-      <c r="K140" t="s">
+      <c r="L140" t="s">
         <v>715</v>
       </c>
-      <c r="L140" t="s">
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="141" spans="1:12">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>717</v>
       </c>
-      <c r="B141" t="s">
-        <v>718</v>
-      </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F141">
         <v>2006</v>
@@ -8714,30 +8719,30 @@
         <v>8565600</v>
       </c>
       <c r="J141" t="s">
+        <v>718</v>
+      </c>
+      <c r="K141" t="s">
         <v>719</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" t="s">
         <v>720</v>
       </c>
-      <c r="L141" t="s">
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="142" spans="1:12">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
         <v>722</v>
       </c>
-      <c r="B142" t="s">
-        <v>723</v>
-      </c>
       <c r="C142" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D142" t="s">
+        <v>80</v>
+      </c>
+      <c r="E142" t="s">
         <v>81</v>
-      </c>
-      <c r="E142" t="s">
-        <v>82</v>
       </c>
       <c r="F142">
         <v>2025</v>
@@ -8752,30 +8757,30 @@
         <v>4482000</v>
       </c>
       <c r="J142" t="s">
+        <v>723</v>
+      </c>
+      <c r="K142" t="s">
         <v>724</v>
       </c>
-      <c r="K142" t="s">
+      <c r="L142" t="s">
         <v>725</v>
       </c>
-      <c r="L142" t="s">
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="143" spans="1:12">
-      <c r="A143" t="s">
+      <c r="B143" t="s">
         <v>727</v>
       </c>
-      <c r="B143" t="s">
-        <v>728</v>
-      </c>
       <c r="C143" t="s">
+        <v>29</v>
+      </c>
+      <c r="D143" t="s">
+        <v>22</v>
+      </c>
+      <c r="E143" t="s">
         <v>30</v>
-      </c>
-      <c r="D143" t="s">
-        <v>23</v>
-      </c>
-      <c r="E143" t="s">
-        <v>31</v>
       </c>
       <c r="F143">
         <v>2006</v>
@@ -8790,30 +8795,30 @@
         <v>4140000</v>
       </c>
       <c r="J143" t="s">
+        <v>728</v>
+      </c>
+      <c r="K143" t="s">
         <v>729</v>
       </c>
-      <c r="K143" t="s">
+      <c r="L143" t="s">
         <v>730</v>
       </c>
-      <c r="L143" t="s">
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="144" spans="1:12">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>732</v>
       </c>
-      <c r="B144" t="s">
-        <v>733</v>
-      </c>
       <c r="C144" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D144" t="s">
+        <v>80</v>
+      </c>
+      <c r="E144" t="s">
         <v>81</v>
-      </c>
-      <c r="E144" t="s">
-        <v>82</v>
       </c>
       <c r="F144">
         <v>2025</v>
@@ -8828,30 +8833,30 @@
         <v>4482000</v>
       </c>
       <c r="J144" t="s">
+        <v>733</v>
+      </c>
+      <c r="K144" t="s">
         <v>734</v>
       </c>
-      <c r="K144" t="s">
+      <c r="L144" t="s">
         <v>735</v>
       </c>
-      <c r="L144" t="s">
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="145" spans="1:12">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>737</v>
       </c>
-      <c r="B145" t="s">
-        <v>738</v>
-      </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D145" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E145" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F145">
         <v>2020</v>
@@ -8866,30 +8871,30 @@
         <v>3950800</v>
       </c>
       <c r="J145" t="s">
+        <v>738</v>
+      </c>
+      <c r="K145" t="s">
         <v>739</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" t="s">
         <v>740</v>
       </c>
-      <c r="L145" t="s">
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="146" spans="1:12">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
         <v>742</v>
       </c>
-      <c r="B146" t="s">
-        <v>743</v>
-      </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E146" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F146">
         <v>2020</v>
@@ -8904,30 +8909,30 @@
         <v>2680900</v>
       </c>
       <c r="J146" t="s">
+        <v>743</v>
+      </c>
+      <c r="K146" t="s">
         <v>744</v>
       </c>
-      <c r="K146" t="s">
+      <c r="L146" t="s">
         <v>745</v>
       </c>
-      <c r="L146" t="s">
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="147" spans="1:12">
-      <c r="A147" t="s">
-        <v>747</v>
-      </c>
       <c r="B147" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F147">
         <v>2018</v>
@@ -8942,21 +8947,21 @@
         <v>2360500</v>
       </c>
       <c r="J147" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K147" t="s">
+        <v>747</v>
+      </c>
+      <c r="L147" t="s">
         <v>748</v>
       </c>
-      <c r="L147" t="s">
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="148" spans="1:12">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>750</v>
-      </c>
-      <c r="B148" t="s">
-        <v>751</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -8965,7 +8970,7 @@
         <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F148">
         <v>2005</v>
@@ -8980,30 +8985,30 @@
         <v>159400</v>
       </c>
       <c r="J148" t="s">
+        <v>751</v>
+      </c>
+      <c r="K148" t="s">
         <v>752</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" t="s">
         <v>753</v>
       </c>
-      <c r="L148" t="s">
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="149" spans="1:12">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
         <v>755</v>
       </c>
-      <c r="B149" t="s">
-        <v>756</v>
-      </c>
       <c r="C149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E149" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F149">
         <v>2025</v>
@@ -9018,30 +9023,30 @@
         <v>2988000</v>
       </c>
       <c r="J149" t="s">
+        <v>756</v>
+      </c>
+      <c r="K149" t="s">
         <v>757</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" t="s">
         <v>758</v>
       </c>
-      <c r="L149" t="s">
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="150" spans="1:12">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
         <v>760</v>
       </c>
-      <c r="B150" t="s">
-        <v>761</v>
-      </c>
       <c r="C150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D150" t="s">
+        <v>108</v>
+      </c>
+      <c r="E150" t="s">
         <v>109</v>
-      </c>
-      <c r="E150" t="s">
-        <v>110</v>
       </c>
       <c r="F150">
         <v>2025</v>
@@ -9056,30 +9061,30 @@
         <v>7470000</v>
       </c>
       <c r="J150" t="s">
+        <v>761</v>
+      </c>
+      <c r="K150" t="s">
         <v>762</v>
       </c>
-      <c r="K150" t="s">
+      <c r="L150" t="s">
         <v>763</v>
       </c>
-      <c r="L150" t="s">
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="151" spans="1:12">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
         <v>765</v>
       </c>
-      <c r="B151" t="s">
-        <v>766</v>
-      </c>
       <c r="C151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F151">
         <v>2025</v>
@@ -9094,30 +9099,30 @@
         <v>3320000</v>
       </c>
       <c r="J151" t="s">
+        <v>766</v>
+      </c>
+      <c r="K151" t="s">
         <v>767</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" t="s">
         <v>768</v>
       </c>
-      <c r="L151" t="s">
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="152" spans="1:12">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
         <v>770</v>
       </c>
-      <c r="B152" t="s">
-        <v>771</v>
-      </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D152" t="s">
         <v>15</v>
       </c>
       <c r="E152" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F152">
         <v>2021</v>
@@ -9132,30 +9137,30 @@
         <v>4236300</v>
       </c>
       <c r="J152" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="K152" t="s">
+        <v>771</v>
+      </c>
+      <c r="L152" t="s">
         <v>772</v>
       </c>
-      <c r="L152" t="s">
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="153" spans="1:12">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
         <v>774</v>
       </c>
-      <c r="B153" t="s">
-        <v>775</v>
-      </c>
       <c r="C153" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D153" t="s">
+        <v>80</v>
+      </c>
+      <c r="E153" t="s">
         <v>81</v>
-      </c>
-      <c r="E153" t="s">
-        <v>82</v>
       </c>
       <c r="F153">
         <v>2008</v>
@@ -9170,30 +9175,30 @@
         <v>2196200</v>
       </c>
       <c r="J153" t="s">
+        <v>775</v>
+      </c>
+      <c r="K153" t="s">
         <v>776</v>
       </c>
-      <c r="K153" t="s">
+      <c r="L153" t="s">
         <v>777</v>
       </c>
-      <c r="L153" t="s">
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="154" spans="1:12">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
         <v>779</v>
       </c>
-      <c r="B154" t="s">
-        <v>780</v>
-      </c>
       <c r="C154" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D154" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" t="s">
         <v>183</v>
-      </c>
-      <c r="E154" t="s">
-        <v>184</v>
       </c>
       <c r="F154">
         <v>2022</v>
@@ -9208,30 +9213,30 @@
         <v>8459400</v>
       </c>
       <c r="J154" t="s">
+        <v>780</v>
+      </c>
+      <c r="K154" t="s">
         <v>781</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" t="s">
         <v>782</v>
       </c>
-      <c r="L154" t="s">
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="155" spans="1:12">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
         <v>784</v>
       </c>
-      <c r="B155" t="s">
-        <v>785</v>
-      </c>
       <c r="C155" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D155" t="s">
+        <v>182</v>
+      </c>
+      <c r="E155" t="s">
         <v>183</v>
-      </c>
-      <c r="E155" t="s">
-        <v>184</v>
       </c>
       <c r="F155">
         <v>2007</v>
@@ -9246,30 +9251,30 @@
         <v>4276200</v>
       </c>
       <c r="J155" t="s">
+        <v>785</v>
+      </c>
+      <c r="K155" t="s">
         <v>786</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" t="s">
         <v>787</v>
       </c>
-      <c r="L155" t="s">
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="156" spans="1:12">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>789</v>
       </c>
-      <c r="B156" t="s">
-        <v>790</v>
-      </c>
       <c r="C156" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F156">
         <v>2006</v>
@@ -9284,30 +9289,30 @@
         <v>2070000</v>
       </c>
       <c r="J156" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K156" t="s">
+        <v>790</v>
+      </c>
+      <c r="L156" t="s">
         <v>791</v>
       </c>
-      <c r="L156" t="s">
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="157" spans="1:12">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>793</v>
-      </c>
-      <c r="B157" t="s">
-        <v>794</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E157" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F157">
         <v>2018</v>
@@ -9322,30 +9327,30 @@
         <v>419600</v>
       </c>
       <c r="J157" t="s">
+        <v>794</v>
+      </c>
+      <c r="K157" t="s">
         <v>795</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" t="s">
         <v>796</v>
       </c>
-      <c r="L157" t="s">
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="158" spans="1:12">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
         <v>798</v>
       </c>
-      <c r="B158" t="s">
-        <v>799</v>
-      </c>
       <c r="C158" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F158">
         <v>2020</v>
@@ -9360,30 +9365,30 @@
         <v>4091900</v>
       </c>
       <c r="J158" t="s">
+        <v>799</v>
+      </c>
+      <c r="K158" t="s">
         <v>800</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" t="s">
         <v>801</v>
       </c>
-      <c r="L158" t="s">
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="159" spans="1:12">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>803</v>
       </c>
-      <c r="B159" t="s">
-        <v>804</v>
-      </c>
       <c r="C159" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D159" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F159">
         <v>2024</v>
@@ -9398,30 +9403,30 @@
         <v>4508600</v>
       </c>
       <c r="J159" t="s">
+        <v>804</v>
+      </c>
+      <c r="K159" t="s">
+        <v>618</v>
+      </c>
+      <c r="L159" t="s">
         <v>805</v>
       </c>
-      <c r="K159" t="s">
-        <v>619</v>
-      </c>
-      <c r="L159" t="s">
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="160" spans="1:12">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>807</v>
-      </c>
-      <c r="B160" t="s">
-        <v>808</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E160" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F160">
         <v>2018</v>
@@ -9436,30 +9441,30 @@
         <v>419600</v>
       </c>
       <c r="J160" t="s">
+        <v>808</v>
+      </c>
+      <c r="K160" t="s">
         <v>809</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" t="s">
         <v>810</v>
       </c>
-      <c r="L160" t="s">
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="161" spans="1:12">
-      <c r="A161" t="s">
+      <c r="B161" t="s">
         <v>812</v>
       </c>
-      <c r="B161" t="s">
-        <v>813</v>
-      </c>
       <c r="C161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D161" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E161" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F161">
         <v>2016</v>
@@ -9474,30 +9479,30 @@
         <v>2908300</v>
       </c>
       <c r="J161" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K161" t="s">
+        <v>813</v>
+      </c>
+      <c r="L161" t="s">
         <v>814</v>
       </c>
-      <c r="L161" t="s">
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="162" spans="1:12">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
         <v>816</v>
       </c>
-      <c r="B162" t="s">
-        <v>817</v>
-      </c>
       <c r="C162" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D162" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E162" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F162">
         <v>2014</v>
@@ -9512,30 +9517,30 @@
         <v>3225400</v>
       </c>
       <c r="J162" t="s">
+        <v>484</v>
+      </c>
+      <c r="K162" t="s">
         <v>485</v>
       </c>
-      <c r="K162" t="s">
-        <v>486</v>
-      </c>
       <c r="L162" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="163" spans="1:12">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>819</v>
       </c>
-      <c r="B163" t="s">
-        <v>820</v>
-      </c>
       <c r="C163" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E163" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F163">
         <v>2011</v>
@@ -9550,30 +9555,30 @@
         <v>2792100</v>
       </c>
       <c r="J163" t="s">
+        <v>820</v>
+      </c>
+      <c r="K163" t="s">
         <v>821</v>
       </c>
-      <c r="K163" t="s">
+      <c r="L163" t="s">
         <v>822</v>
       </c>
-      <c r="L163" t="s">
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="164" spans="1:12">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
         <v>824</v>
       </c>
-      <c r="B164" t="s">
-        <v>825</v>
-      </c>
       <c r="C164" t="s">
+        <v>36</v>
+      </c>
+      <c r="D164" t="s">
+        <v>22</v>
+      </c>
+      <c r="E164" t="s">
         <v>37</v>
-      </c>
-      <c r="D164" t="s">
-        <v>23</v>
-      </c>
-      <c r="E164" t="s">
-        <v>38</v>
       </c>
       <c r="F164">
         <v>2006</v>
@@ -9588,30 +9593,30 @@
         <v>2569700</v>
       </c>
       <c r="J164" t="s">
+        <v>825</v>
+      </c>
+      <c r="K164" t="s">
         <v>826</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" t="s">
         <v>827</v>
       </c>
-      <c r="L164" t="s">
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="165" spans="1:12">
-      <c r="A165" t="s">
+      <c r="B165" t="s">
         <v>829</v>
-      </c>
-      <c r="B165" t="s">
-        <v>830</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
       </c>
       <c r="D165" t="s">
+        <v>56</v>
+      </c>
+      <c r="E165" t="s">
         <v>57</v>
-      </c>
-      <c r="E165" t="s">
-        <v>58</v>
       </c>
       <c r="F165">
         <v>2018</v>
@@ -9626,30 +9631,30 @@
         <v>498300</v>
       </c>
       <c r="J165" t="s">
+        <v>830</v>
+      </c>
+      <c r="K165" t="s">
         <v>831</v>
       </c>
-      <c r="K165" t="s">
+      <c r="L165" t="s">
         <v>832</v>
       </c>
-      <c r="L165" t="s">
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="166" spans="1:12">
-      <c r="A166" t="s">
+      <c r="B166" t="s">
         <v>834</v>
       </c>
-      <c r="B166" t="s">
-        <v>835</v>
-      </c>
       <c r="C166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E166" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F166">
         <v>2011</v>
@@ -9664,21 +9669,21 @@
         <v>1733000</v>
       </c>
       <c r="J166" t="s">
+        <v>835</v>
+      </c>
+      <c r="K166" t="s">
         <v>836</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" t="s">
         <v>837</v>
       </c>
-      <c r="L166" t="s">
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="167" spans="1:12">
-      <c r="A167" t="s">
+      <c r="B167" t="s">
         <v>839</v>
-      </c>
-      <c r="B167" t="s">
-        <v>840</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
@@ -9687,7 +9692,7 @@
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F167">
         <v>2017</v>
@@ -9702,30 +9707,30 @@
         <v>302800</v>
       </c>
       <c r="J167" t="s">
+        <v>840</v>
+      </c>
+      <c r="K167" t="s">
         <v>841</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" t="s">
         <v>842</v>
       </c>
-      <c r="L167" t="s">
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="168" spans="1:12">
-      <c r="A168" t="s">
+      <c r="B168" t="s">
         <v>844</v>
       </c>
-      <c r="B168" t="s">
-        <v>845</v>
-      </c>
       <c r="C168" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D168" t="s">
+        <v>289</v>
+      </c>
+      <c r="E168" t="s">
         <v>290</v>
-      </c>
-      <c r="E168" t="s">
-        <v>291</v>
       </c>
       <c r="F168">
         <v>2012</v>
@@ -9740,30 +9745,30 @@
         <v>3420600</v>
       </c>
       <c r="J168" t="s">
+        <v>513</v>
+      </c>
+      <c r="K168" t="s">
         <v>514</v>
       </c>
-      <c r="K168" t="s">
-        <v>515</v>
-      </c>
       <c r="L168" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="169" spans="1:12">
-      <c r="A169" t="s">
+      <c r="B169" t="s">
         <v>847</v>
       </c>
-      <c r="B169" t="s">
-        <v>848</v>
-      </c>
       <c r="C169" t="s">
+        <v>29</v>
+      </c>
+      <c r="D169" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" t="s">
         <v>30</v>
-      </c>
-      <c r="D169" t="s">
-        <v>23</v>
-      </c>
-      <c r="E169" t="s">
-        <v>31</v>
       </c>
       <c r="F169">
         <v>2013</v>
@@ -9778,30 +9783,30 @@
         <v>6161900</v>
       </c>
       <c r="J169" t="s">
+        <v>848</v>
+      </c>
+      <c r="K169" t="s">
         <v>849</v>
       </c>
-      <c r="K169" t="s">
+      <c r="L169" t="s">
         <v>850</v>
       </c>
-      <c r="L169" t="s">
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="170" spans="1:12">
-      <c r="A170" t="s">
+      <c r="B170" t="s">
         <v>852</v>
-      </c>
-      <c r="B170" t="s">
-        <v>853</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
       </c>
       <c r="D170" t="s">
+        <v>56</v>
+      </c>
+      <c r="E170" t="s">
         <v>57</v>
-      </c>
-      <c r="E170" t="s">
-        <v>58</v>
       </c>
       <c r="F170">
         <v>2015</v>
@@ -9816,30 +9821,30 @@
         <v>441600</v>
       </c>
       <c r="J170" t="s">
+        <v>279</v>
+      </c>
+      <c r="K170" t="s">
         <v>280</v>
       </c>
-      <c r="K170" t="s">
-        <v>281</v>
-      </c>
       <c r="L170" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="171" spans="1:12">
-      <c r="A171" t="s">
+      <c r="B171" t="s">
         <v>855</v>
       </c>
-      <c r="B171" t="s">
-        <v>856</v>
-      </c>
       <c r="C171" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D171" t="s">
+        <v>200</v>
+      </c>
+      <c r="E171" t="s">
         <v>201</v>
-      </c>
-      <c r="E171" t="s">
-        <v>202</v>
       </c>
       <c r="F171">
         <v>2021</v>
@@ -9854,30 +9859,30 @@
         <v>2483400</v>
       </c>
       <c r="J171" t="s">
+        <v>856</v>
+      </c>
+      <c r="K171" t="s">
         <v>857</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" t="s">
         <v>858</v>
       </c>
-      <c r="L171" t="s">
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="172" spans="1:12">
-      <c r="A172" t="s">
-        <v>860</v>
-      </c>
       <c r="B172" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C172" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D172" t="s">
+        <v>289</v>
+      </c>
+      <c r="E172" t="s">
         <v>290</v>
-      </c>
-      <c r="E172" t="s">
-        <v>291</v>
       </c>
       <c r="F172">
         <v>2011</v>
@@ -9892,30 +9897,30 @@
         <v>3252300</v>
       </c>
       <c r="J172" t="s">
+        <v>860</v>
+      </c>
+      <c r="K172" t="s">
         <v>861</v>
       </c>
-      <c r="K172" t="s">
+      <c r="L172" t="s">
         <v>862</v>
       </c>
-      <c r="L172" t="s">
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="173" spans="1:12">
-      <c r="A173" t="s">
+      <c r="B173" t="s">
         <v>864</v>
       </c>
-      <c r="B173" t="s">
-        <v>865</v>
-      </c>
       <c r="C173" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D173" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E173" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F173">
         <v>2012</v>
@@ -9930,21 +9935,21 @@
         <v>2835300</v>
       </c>
       <c r="J173" t="s">
+        <v>865</v>
+      </c>
+      <c r="K173" t="s">
         <v>866</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" t="s">
         <v>867</v>
       </c>
-      <c r="L173" t="s">
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="174" spans="1:12">
-      <c r="A174" t="s">
+      <c r="B174" t="s">
         <v>869</v>
-      </c>
-      <c r="B174" t="s">
-        <v>870</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
@@ -9968,30 +9973,30 @@
         <v>289800</v>
       </c>
       <c r="J174" t="s">
+        <v>870</v>
+      </c>
+      <c r="K174" t="s">
         <v>871</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" t="s">
         <v>872</v>
       </c>
-      <c r="L174" t="s">
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="175" spans="1:12">
-      <c r="A175" t="s">
+      <c r="B175" t="s">
         <v>874</v>
       </c>
-      <c r="B175" t="s">
-        <v>875</v>
-      </c>
       <c r="C175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D175" t="s">
+        <v>108</v>
+      </c>
+      <c r="E175" t="s">
         <v>109</v>
-      </c>
-      <c r="E175" t="s">
-        <v>110</v>
       </c>
       <c r="F175">
         <v>2025</v>
@@ -10006,30 +10011,30 @@
         <v>7470000</v>
       </c>
       <c r="J175" t="s">
+        <v>875</v>
+      </c>
+      <c r="K175" t="s">
         <v>876</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" t="s">
         <v>877</v>
       </c>
-      <c r="L175" t="s">
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="176" spans="1:12">
-      <c r="A176" t="s">
+      <c r="B176" t="s">
         <v>879</v>
       </c>
-      <c r="B176" t="s">
-        <v>880</v>
-      </c>
       <c r="C176" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E176" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F176">
         <v>2023</v>
@@ -10044,30 +10049,30 @@
         <v>4525200</v>
       </c>
       <c r="J176" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K176" t="s">
+        <v>880</v>
+      </c>
+      <c r="L176" t="s">
         <v>881</v>
       </c>
-      <c r="L176" t="s">
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="177" spans="1:12">
-      <c r="A177" t="s">
+      <c r="B177" t="s">
         <v>883</v>
       </c>
-      <c r="B177" t="s">
-        <v>884</v>
-      </c>
       <c r="C177" t="s">
+        <v>21</v>
+      </c>
+      <c r="D177" t="s">
         <v>22</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>23</v>
-      </c>
-      <c r="E177" t="s">
-        <v>24</v>
       </c>
       <c r="F177">
         <v>2023</v>
@@ -10082,30 +10087,30 @@
         <v>3432900</v>
       </c>
       <c r="J177" t="s">
+        <v>884</v>
+      </c>
+      <c r="K177" t="s">
         <v>885</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" t="s">
         <v>886</v>
       </c>
-      <c r="L177" t="s">
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="178" spans="1:12">
-      <c r="A178" t="s">
+      <c r="B178" t="s">
         <v>888</v>
       </c>
-      <c r="B178" t="s">
-        <v>889</v>
-      </c>
       <c r="C178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D178" t="s">
+        <v>289</v>
+      </c>
+      <c r="E178" t="s">
         <v>290</v>
-      </c>
-      <c r="E178" t="s">
-        <v>291</v>
       </c>
       <c r="F178">
         <v>2014</v>
@@ -10120,30 +10125,30 @@
         <v>3757100</v>
       </c>
       <c r="J178" t="s">
+        <v>889</v>
+      </c>
+      <c r="K178" t="s">
         <v>890</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" t="s">
         <v>891</v>
       </c>
-      <c r="L178" t="s">
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="179" spans="1:12">
-      <c r="A179" t="s">
+      <c r="B179" t="s">
         <v>893</v>
-      </c>
-      <c r="B179" t="s">
-        <v>894</v>
       </c>
       <c r="C179" t="s">
         <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E179" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F179">
         <v>2011</v>
@@ -10158,30 +10163,30 @@
         <v>308100</v>
       </c>
       <c r="J179" t="s">
+        <v>894</v>
+      </c>
+      <c r="K179" t="s">
         <v>895</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" t="s">
         <v>896</v>
       </c>
-      <c r="L179" t="s">
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="180" spans="1:12">
-      <c r="A180" t="s">
+      <c r="B180" t="s">
         <v>898</v>
       </c>
-      <c r="B180" t="s">
-        <v>899</v>
-      </c>
       <c r="C180" t="s">
+        <v>36</v>
+      </c>
+      <c r="D180" t="s">
+        <v>22</v>
+      </c>
+      <c r="E180" t="s">
         <v>37</v>
-      </c>
-      <c r="D180" t="s">
-        <v>23</v>
-      </c>
-      <c r="E180" t="s">
-        <v>38</v>
       </c>
       <c r="F180">
         <v>2022</v>
@@ -10196,30 +10201,30 @@
         <v>5438200</v>
       </c>
       <c r="J180" t="s">
+        <v>899</v>
+      </c>
+      <c r="K180" t="s">
         <v>900</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" t="s">
         <v>901</v>
       </c>
-      <c r="L180" t="s">
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="181" spans="1:12">
-      <c r="A181" t="s">
+      <c r="B181" t="s">
         <v>903</v>
       </c>
-      <c r="B181" t="s">
-        <v>904</v>
-      </c>
       <c r="C181" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D181" t="s">
+        <v>289</v>
+      </c>
+      <c r="E181" t="s">
         <v>290</v>
-      </c>
-      <c r="E181" t="s">
-        <v>291</v>
       </c>
       <c r="F181">
         <v>2019</v>
@@ -10234,21 +10239,21 @@
         <v>4598200</v>
       </c>
       <c r="J181" t="s">
+        <v>904</v>
+      </c>
+      <c r="K181" t="s">
         <v>905</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" t="s">
         <v>906</v>
       </c>
-      <c r="L181" t="s">
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="182" spans="1:12">
-      <c r="A182" t="s">
+      <c r="B182" t="s">
         <v>908</v>
-      </c>
-      <c r="B182" t="s">
-        <v>909</v>
       </c>
       <c r="C182" t="s">
         <v>14</v>
@@ -10257,7 +10262,7 @@
         <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F182">
         <v>2018</v>
@@ -10272,30 +10277,30 @@
         <v>275400</v>
       </c>
       <c r="J182" t="s">
+        <v>909</v>
+      </c>
+      <c r="K182" t="s">
         <v>910</v>
       </c>
-      <c r="K182" t="s">
+      <c r="L182" t="s">
         <v>911</v>
       </c>
-      <c r="L182" t="s">
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="183" spans="1:12">
-      <c r="A183" t="s">
-        <v>913</v>
-      </c>
       <c r="B183" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C183" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E183" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F183">
         <v>2025</v>
@@ -10310,30 +10315,30 @@
         <v>2988000</v>
       </c>
       <c r="J183" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K183" t="s">
+        <v>913</v>
+      </c>
+      <c r="L183" t="s">
         <v>914</v>
       </c>
-      <c r="L183" t="s">
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="184" spans="1:12">
-      <c r="A184" t="s">
+      <c r="B184" t="s">
         <v>916</v>
       </c>
-      <c r="B184" t="s">
-        <v>917</v>
-      </c>
       <c r="C184" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D184" t="s">
+        <v>200</v>
+      </c>
+      <c r="E184" t="s">
         <v>201</v>
-      </c>
-      <c r="E184" t="s">
-        <v>202</v>
       </c>
       <c r="F184">
         <v>2018</v>
@@ -10348,30 +10353,30 @@
         <v>2229400</v>
       </c>
       <c r="J184" t="s">
+        <v>917</v>
+      </c>
+      <c r="K184" t="s">
         <v>918</v>
       </c>
-      <c r="K184" t="s">
+      <c r="L184" t="s">
         <v>919</v>
       </c>
-      <c r="L184" t="s">
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="185" spans="1:12">
-      <c r="A185" t="s">
+      <c r="B185" t="s">
         <v>921</v>
       </c>
-      <c r="B185" t="s">
-        <v>922</v>
-      </c>
       <c r="C185" t="s">
+        <v>36</v>
+      </c>
+      <c r="D185" t="s">
+        <v>22</v>
+      </c>
+      <c r="E185" t="s">
         <v>37</v>
-      </c>
-      <c r="D185" t="s">
-        <v>23</v>
-      </c>
-      <c r="E185" t="s">
-        <v>38</v>
       </c>
       <c r="F185">
         <v>2017</v>
@@ -10386,30 +10391,30 @@
         <v>4541800</v>
       </c>
       <c r="J185" t="s">
+        <v>922</v>
+      </c>
+      <c r="K185" t="s">
         <v>923</v>
       </c>
-      <c r="K185" t="s">
+      <c r="L185" t="s">
         <v>924</v>
       </c>
-      <c r="L185" t="s">
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="186" spans="1:12">
-      <c r="A186" t="s">
+      <c r="B186" t="s">
         <v>926</v>
       </c>
-      <c r="B186" t="s">
-        <v>927</v>
-      </c>
       <c r="C186" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D186" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E186" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F186">
         <v>2005</v>
@@ -10424,30 +10429,30 @@
         <v>1925600</v>
       </c>
       <c r="J186" t="s">
+        <v>927</v>
+      </c>
+      <c r="K186" t="s">
         <v>928</v>
       </c>
-      <c r="K186" t="s">
+      <c r="L186" t="s">
         <v>929</v>
       </c>
-      <c r="L186" t="s">
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="187" spans="1:12">
-      <c r="A187" t="s">
+      <c r="B187" t="s">
         <v>931</v>
-      </c>
-      <c r="B187" t="s">
-        <v>932</v>
       </c>
       <c r="C187" t="s">
         <v>14</v>
       </c>
       <c r="D187" t="s">
+        <v>68</v>
+      </c>
+      <c r="E187" t="s">
         <v>69</v>
-      </c>
-      <c r="E187" t="s">
-        <v>70</v>
       </c>
       <c r="F187">
         <v>2008</v>
@@ -10462,30 +10467,30 @@
         <v>130100</v>
       </c>
       <c r="J187" t="s">
+        <v>932</v>
+      </c>
+      <c r="K187" t="s">
+        <v>857</v>
+      </c>
+      <c r="L187" t="s">
         <v>933</v>
       </c>
-      <c r="K187" t="s">
-        <v>858</v>
-      </c>
-      <c r="L187" t="s">
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="188" spans="1:12">
-      <c r="A188" t="s">
-        <v>935</v>
-      </c>
       <c r="B188" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C188" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D188" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E188" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F188">
         <v>2025</v>
@@ -10500,30 +10505,30 @@
         <v>4648000</v>
       </c>
       <c r="J188" t="s">
+        <v>935</v>
+      </c>
+      <c r="K188" t="s">
         <v>936</v>
       </c>
-      <c r="K188" t="s">
+      <c r="L188" t="s">
         <v>937</v>
       </c>
-      <c r="L188" t="s">
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="189" spans="1:12">
-      <c r="A189" t="s">
-        <v>939</v>
-      </c>
       <c r="B189" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C189" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D189" t="s">
+        <v>182</v>
+      </c>
+      <c r="E189" t="s">
         <v>183</v>
-      </c>
-      <c r="E189" t="s">
-        <v>184</v>
       </c>
       <c r="F189">
         <v>2022</v>
@@ -10538,30 +10543,30 @@
         <v>8459400</v>
       </c>
       <c r="J189" t="s">
+        <v>939</v>
+      </c>
+      <c r="K189" t="s">
         <v>940</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" t="s">
         <v>941</v>
       </c>
-      <c r="L189" t="s">
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="190" spans="1:12">
-      <c r="A190" t="s">
+      <c r="B190" t="s">
         <v>943</v>
       </c>
-      <c r="B190" t="s">
-        <v>944</v>
-      </c>
       <c r="C190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E190" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F190">
         <v>2016</v>
@@ -10576,30 +10581,30 @@
         <v>14541600</v>
       </c>
       <c r="J190" t="s">
+        <v>944</v>
+      </c>
+      <c r="K190" t="s">
         <v>945</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" t="s">
         <v>946</v>
       </c>
-      <c r="L190" t="s">
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="191" spans="1:12">
-      <c r="A191" t="s">
+      <c r="B191" t="s">
         <v>948</v>
       </c>
-      <c r="B191" t="s">
-        <v>949</v>
-      </c>
       <c r="C191" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D191" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E191" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F191">
         <v>2008</v>
@@ -10614,30 +10619,30 @@
         <v>2358900</v>
       </c>
       <c r="J191" t="s">
+        <v>949</v>
+      </c>
+      <c r="K191" t="s">
+        <v>866</v>
+      </c>
+      <c r="L191" t="s">
         <v>950</v>
       </c>
-      <c r="K191" t="s">
-        <v>867</v>
-      </c>
-      <c r="L191" t="s">
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="192" spans="1:12">
-      <c r="A192" t="s">
+      <c r="B192" t="s">
         <v>952</v>
       </c>
-      <c r="B192" t="s">
-        <v>953</v>
-      </c>
       <c r="C192" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D192" t="s">
+        <v>182</v>
+      </c>
+      <c r="E192" t="s">
         <v>183</v>
-      </c>
-      <c r="E192" t="s">
-        <v>184</v>
       </c>
       <c r="F192">
         <v>2023</v>
@@ -10652,30 +10657,30 @@
         <v>8738200</v>
       </c>
       <c r="J192" t="s">
+        <v>953</v>
+      </c>
+      <c r="K192" t="s">
         <v>954</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" t="s">
         <v>955</v>
       </c>
-      <c r="L192" t="s">
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="193" spans="1:12">
-      <c r="A193" t="s">
+      <c r="B193" t="s">
         <v>957</v>
       </c>
-      <c r="B193" t="s">
-        <v>958</v>
-      </c>
       <c r="C193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D193" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E193" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F193">
         <v>2012</v>
@@ -10690,30 +10695,30 @@
         <v>2430200</v>
       </c>
       <c r="J193" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K193" t="s">
+        <v>958</v>
+      </c>
+      <c r="L193" t="s">
         <v>959</v>
       </c>
-      <c r="L193" t="s">
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="194" spans="1:12">
-      <c r="A194" t="s">
+      <c r="B194" t="s">
         <v>961</v>
       </c>
-      <c r="B194" t="s">
-        <v>962</v>
-      </c>
       <c r="C194" t="s">
+        <v>21</v>
+      </c>
+      <c r="D194" t="s">
         <v>22</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>23</v>
-      </c>
-      <c r="E194" t="s">
-        <v>24</v>
       </c>
       <c r="F194">
         <v>2019</v>
@@ -10728,30 +10733,30 @@
         <v>2994600</v>
       </c>
       <c r="J194" t="s">
+        <v>962</v>
+      </c>
+      <c r="K194" t="s">
         <v>963</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" t="s">
         <v>964</v>
       </c>
-      <c r="L194" t="s">
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="195" spans="1:12">
-      <c r="A195" t="s">
+      <c r="B195" t="s">
         <v>966</v>
       </c>
-      <c r="B195" t="s">
-        <v>967</v>
-      </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
       </c>
       <c r="E195" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F195">
         <v>2019</v>
@@ -10766,30 +10771,30 @@
         <v>6533800</v>
       </c>
       <c r="J195" t="s">
+        <v>922</v>
+      </c>
+      <c r="K195" t="s">
         <v>923</v>
       </c>
-      <c r="K195" t="s">
-        <v>924</v>
-      </c>
       <c r="L195" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="196" spans="1:12">
-      <c r="A196" t="s">
-        <v>969</v>
-      </c>
       <c r="B196" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C196" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D196" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E196" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F196">
         <v>2006</v>
@@ -10804,30 +10809,30 @@
         <v>8565600</v>
       </c>
       <c r="J196" t="s">
+        <v>969</v>
+      </c>
+      <c r="K196" t="s">
         <v>970</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" t="s">
         <v>971</v>
       </c>
-      <c r="L196" t="s">
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="197" spans="1:12">
-      <c r="A197" t="s">
+      <c r="B197" t="s">
         <v>973</v>
       </c>
-      <c r="B197" t="s">
-        <v>974</v>
-      </c>
       <c r="C197" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D197" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E197" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F197">
         <v>2018</v>
@@ -10842,30 +10847,30 @@
         <v>2360500</v>
       </c>
       <c r="J197" t="s">
+        <v>974</v>
+      </c>
+      <c r="K197" t="s">
         <v>975</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" t="s">
         <v>976</v>
       </c>
-      <c r="L197" t="s">
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="198" spans="1:12">
-      <c r="A198" t="s">
+      <c r="B198" t="s">
         <v>978</v>
       </c>
-      <c r="B198" t="s">
-        <v>979</v>
-      </c>
       <c r="C198" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D198" t="s">
+        <v>108</v>
+      </c>
+      <c r="E198" t="s">
         <v>109</v>
-      </c>
-      <c r="E198" t="s">
-        <v>110</v>
       </c>
       <c r="F198">
         <v>2015</v>
@@ -10880,30 +10885,30 @@
         <v>5229000</v>
       </c>
       <c r="J198" t="s">
+        <v>979</v>
+      </c>
+      <c r="K198" t="s">
         <v>980</v>
       </c>
-      <c r="K198" t="s">
+      <c r="L198" t="s">
         <v>981</v>
       </c>
-      <c r="L198" t="s">
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="199" spans="1:12">
-      <c r="A199" t="s">
+      <c r="B199" t="s">
         <v>983</v>
       </c>
-      <c r="B199" t="s">
-        <v>984</v>
-      </c>
       <c r="C199" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D199" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E199" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F199">
         <v>2020</v>
@@ -10918,30 +10923,30 @@
         <v>3950800</v>
       </c>
       <c r="J199" t="s">
+        <v>984</v>
+      </c>
+      <c r="K199" t="s">
         <v>985</v>
       </c>
-      <c r="K199" t="s">
+      <c r="L199" t="s">
         <v>986</v>
       </c>
-      <c r="L199" t="s">
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="200" spans="1:12">
-      <c r="A200" t="s">
+      <c r="B200" t="s">
         <v>988</v>
       </c>
-      <c r="B200" t="s">
-        <v>989</v>
-      </c>
       <c r="C200" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E200" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F200">
         <v>2015</v>
@@ -10956,30 +10961,30 @@
         <v>2091600</v>
       </c>
       <c r="J200" t="s">
+        <v>989</v>
+      </c>
+      <c r="K200" t="s">
         <v>990</v>
       </c>
-      <c r="K200" t="s">
+      <c r="L200" t="s">
         <v>991</v>
       </c>
-      <c r="L200" t="s">
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="201" spans="1:12">
-      <c r="A201" t="s">
+      <c r="B201" t="s">
         <v>993</v>
       </c>
-      <c r="B201" t="s">
-        <v>994</v>
-      </c>
       <c r="C201" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E201" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F201">
         <v>2025</v>
@@ -10994,27 +10999,16 @@
         <v>2988000</v>
       </c>
       <c r="J201" t="s">
+        <v>994</v>
+      </c>
+      <c r="K201" t="s">
         <v>995</v>
       </c>
-      <c r="K201" t="s">
+      <c r="L201" t="s">
         <v>996</v>
       </c>
-      <c r="L201" t="s">
-        <v>997</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/template_impor_pajak.xlsx
+++ b/template_impor_pajak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\2026-05-tagih-pajak\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8133D753-E326-4A45-8D5A-E750A8082E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6700D5E7-F943-4FA6-BF20-7FC4DD0AD737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2352" yWindow="960" windowWidth="20232" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="990">
   <si>
     <t>NOPOL</t>
   </si>
@@ -76,9 +76,6 @@
     <t>27/02/2026</t>
   </si>
   <si>
-    <t>27/02/2031</t>
-  </si>
-  <si>
     <t>P 3110 SE</t>
   </si>
   <si>
@@ -94,12 +91,6 @@
     <t>VIOS 1.5 G</t>
   </si>
   <si>
-    <t>23/06/2026</t>
-  </si>
-  <si>
-    <t>23/06/2031</t>
-  </si>
-  <si>
     <t>08122264686</t>
   </si>
   <si>
@@ -115,12 +106,6 @@
     <t>FORTUNER 2.8 VRZ</t>
   </si>
   <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
-    <t>16/04/2031</t>
-  </si>
-  <si>
     <t>08525789968</t>
   </si>
   <si>
@@ -136,12 +121,6 @@
     <t>INNOVA REBORN 2.4</t>
   </si>
   <si>
-    <t>14/08/2025</t>
-  </si>
-  <si>
-    <t>14/08/2029</t>
-  </si>
-  <si>
     <t>08783839641</t>
   </si>
   <si>
@@ -197,9 +176,6 @@
   </si>
   <si>
     <t>20/09/2025</t>
-  </si>
-  <si>
-    <t>20/09/2029</t>
   </si>
   <si>
     <t>08135954520</t>
@@ -3047,9 +3023,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3436,31 +3413,31 @@
       <c r="I2">
         <v>245000</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="J2" s="2">
+        <v>46080</v>
+      </c>
+      <c r="K2" s="2">
+        <v>47906</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>2018</v>
@@ -3474,31 +3451,31 @@
       <c r="I3">
         <v>2885100</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
+      <c r="J3" s="2">
+        <v>46196</v>
+      </c>
+      <c r="K3" s="2">
+        <v>48022</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
       </c>
       <c r="F4">
         <v>2009</v>
@@ -3512,31 +3489,31 @@
       <c r="I4">
         <v>5006600</v>
       </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
+      <c r="J4" s="2">
+        <v>46128</v>
+      </c>
+      <c r="K4" s="2">
+        <v>47954</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>2020</v>
@@ -3550,31 +3527,31 @@
       <c r="I5">
         <v>5079600</v>
       </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" t="s">
-        <v>39</v>
+      <c r="J5" s="2">
+        <v>45883</v>
+      </c>
+      <c r="K5" s="2">
+        <v>47344</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>2023</v>
@@ -3589,30 +3566,30 @@
         <v>4681200</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>2008</v>
@@ -3627,30 +3604,30 @@
         <v>2928200</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>2013</v>
@@ -3665,30 +3642,30 @@
         <v>403700</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" t="s">
-        <v>59</v>
+        <v>51</v>
+      </c>
+      <c r="K8" s="2">
+        <v>47381</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>2010</v>
@@ -3703,30 +3680,30 @@
         <v>3286800</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F10">
         <v>2008</v>
@@ -3741,30 +3718,30 @@
         <v>130100</v>
       </c>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
       </c>
       <c r="F11">
         <v>2019</v>
@@ -3779,30 +3756,30 @@
         <v>2994600</v>
       </c>
       <c r="J11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F12">
         <v>2024</v>
@@ -3817,30 +3794,30 @@
         <v>4347500</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="L12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>22</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
       </c>
       <c r="F13">
         <v>2019</v>
@@ -3855,30 +3832,30 @@
         <v>2994600</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F14">
         <v>2008</v>
@@ -3893,30 +3870,30 @@
         <v>309100</v>
       </c>
       <c r="J14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="L14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F15">
         <v>2006</v>
@@ -3931,30 +3908,30 @@
         <v>2070000</v>
       </c>
       <c r="J15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
       </c>
       <c r="F16">
         <v>2012</v>
@@ -3969,30 +3946,30 @@
         <v>2227700</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="L16" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F17">
         <v>2008</v>
@@ -4007,30 +3984,30 @@
         <v>3660300</v>
       </c>
       <c r="J17" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F18">
         <v>2022</v>
@@ -4045,30 +4022,30 @@
         <v>4229700</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F19">
         <v>2007</v>
@@ -4083,30 +4060,30 @@
         <v>244400</v>
       </c>
       <c r="J19" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K19" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F20">
         <v>2010</v>
@@ -4121,30 +4098,30 @@
         <v>155200</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F21">
         <v>2025</v>
@@ -4159,30 +4136,30 @@
         <v>3320000</v>
       </c>
       <c r="J21" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K21" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>22</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
       </c>
       <c r="F22">
         <v>2022</v>
@@ -4197,30 +4174,30 @@
         <v>3323300</v>
       </c>
       <c r="J22" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K22" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F23">
         <v>2025</v>
@@ -4235,30 +4212,30 @@
         <v>19920000</v>
       </c>
       <c r="J23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="K23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F24">
         <v>2014</v>
@@ -4273,30 +4250,30 @@
         <v>2113200</v>
       </c>
       <c r="J24" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="K24" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F25">
         <v>2018</v>
@@ -4311,30 +4288,30 @@
         <v>5901300</v>
       </c>
       <c r="J25" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="K25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="L25" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F26">
         <v>2010</v>
@@ -4349,30 +4326,30 @@
         <v>2647700</v>
       </c>
       <c r="J26" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="K26" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="L26" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F27">
         <v>2023</v>
@@ -4387,30 +4364,30 @@
         <v>249700</v>
       </c>
       <c r="J27" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K27" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F28">
         <v>2007</v>
@@ -4425,30 +4402,30 @@
         <v>2290800</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F29">
         <v>2023</v>
@@ -4463,30 +4440,30 @@
         <v>249700</v>
       </c>
       <c r="J29" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K29" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L29" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F30">
         <v>2025</v>
@@ -4501,30 +4478,30 @@
         <v>9296000</v>
       </c>
       <c r="J30" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="K30" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="L30" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F31">
         <v>2022</v>
@@ -4539,21 +4516,21 @@
         <v>4531800</v>
       </c>
       <c r="J31" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="K31" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L31" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -4562,7 +4539,7 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F32">
         <v>2021</v>
@@ -4577,30 +4554,30 @@
         <v>350600</v>
       </c>
       <c r="J32" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="K32" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F33">
         <v>2011</v>
@@ -4615,21 +4592,21 @@
         <v>1636800</v>
       </c>
       <c r="J33" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="K33" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L33" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -4638,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F34">
         <v>2023</v>
@@ -4653,30 +4630,30 @@
         <v>327700</v>
       </c>
       <c r="J34" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K34" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F35">
         <v>2025</v>
@@ -4691,21 +4668,21 @@
         <v>19920000</v>
       </c>
       <c r="J35" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="K35" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -4714,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F36">
         <v>2021</v>
@@ -4729,30 +4706,30 @@
         <v>350600</v>
       </c>
       <c r="J36" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K36" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L36" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F37">
         <v>2017</v>
@@ -4767,30 +4744,30 @@
         <v>4541800</v>
       </c>
       <c r="J37" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="K37" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="L37" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E38" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F38">
         <v>2008</v>
@@ -4805,30 +4782,30 @@
         <v>4555000</v>
       </c>
       <c r="J38" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K38" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L38" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F39">
         <v>2020</v>
@@ -4843,30 +4820,30 @@
         <v>8183800</v>
       </c>
       <c r="J39" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K39" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="L39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F40">
         <v>2023</v>
@@ -4881,30 +4858,30 @@
         <v>7489900</v>
       </c>
       <c r="J40" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="K40" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L40" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F41">
         <v>2011</v>
@@ -4919,30 +4896,30 @@
         <v>3466100</v>
       </c>
       <c r="J41" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="K41" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="L41" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B42" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F42">
         <v>2005</v>
@@ -4957,30 +4934,30 @@
         <v>1925600</v>
       </c>
       <c r="J42" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K42" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L42" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F43">
         <v>2009</v>
@@ -4995,30 +4972,30 @@
         <v>3107500</v>
       </c>
       <c r="J43" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="K43" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="L43" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F44">
         <v>2014</v>
@@ -5033,30 +5010,30 @@
         <v>3002900</v>
       </c>
       <c r="J44" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="K44" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="L44" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F45">
         <v>2017</v>
@@ -5071,21 +5048,21 @@
         <v>15139200</v>
       </c>
       <c r="J45" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="K45" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="L45" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -5094,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F46">
         <v>2010</v>
@@ -5109,30 +5086,30 @@
         <v>191700</v>
       </c>
       <c r="J46" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K46" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="L46" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F47">
         <v>2019</v>
@@ -5147,30 +5124,30 @@
         <v>3266900</v>
       </c>
       <c r="J47" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="K47" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="L47" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F48">
         <v>2010</v>
@@ -5185,30 +5162,30 @@
         <v>4382400</v>
       </c>
       <c r="J48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="K48" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="L48" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F49">
         <v>2023</v>
@@ -5223,30 +5200,30 @@
         <v>2964800</v>
       </c>
       <c r="J49" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="K49" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="L49" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C50" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E50" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F50">
         <v>2022</v>
@@ -5261,30 +5238,30 @@
         <v>5102800</v>
       </c>
       <c r="J50" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="K50" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="L50" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B51" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F51">
         <v>2020</v>
@@ -5299,30 +5276,30 @@
         <v>3809700</v>
       </c>
       <c r="J51" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="K51" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="L51" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F52">
         <v>2023</v>
@@ -5337,30 +5314,30 @@
         <v>7489900</v>
       </c>
       <c r="J52" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="K52" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L52" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B53" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F53">
         <v>2017</v>
@@ -5375,30 +5352,30 @@
         <v>5677200</v>
       </c>
       <c r="J53" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="K53" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="L53" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B54" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E54" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F54">
         <v>2009</v>
@@ -5413,30 +5390,30 @@
         <v>1640100</v>
       </c>
       <c r="J54" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="K54" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="L54" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F55">
         <v>2022</v>
@@ -5451,30 +5428,30 @@
         <v>6797700</v>
       </c>
       <c r="J55" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="K55" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="L55" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B56" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F56">
         <v>2010</v>
@@ -5489,30 +5466,30 @@
         <v>2465100</v>
       </c>
       <c r="J56" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="K56" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="L56" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B57" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F57">
         <v>2012</v>
@@ -5527,30 +5504,30 @@
         <v>1822700</v>
       </c>
       <c r="J57" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="K57" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="L57" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B58" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F58">
         <v>2007</v>
@@ -5565,30 +5542,30 @@
         <v>1374500</v>
       </c>
       <c r="J58" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K58" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="L58" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E59" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F59">
         <v>2023</v>
@@ -5603,30 +5580,30 @@
         <v>8738200</v>
       </c>
       <c r="J59" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K59" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L59" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B60" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E60" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F60">
         <v>2021</v>
@@ -5641,21 +5618,21 @@
         <v>6573600</v>
       </c>
       <c r="J60" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="K60" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L60" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B61" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -5679,30 +5656,30 @@
         <v>209200</v>
       </c>
       <c r="J61" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="K61" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L61" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B62" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" t="s">
         <v>21</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>22</v>
-      </c>
-      <c r="E62" t="s">
-        <v>23</v>
       </c>
       <c r="F62">
         <v>2012</v>
@@ -5717,30 +5694,30 @@
         <v>2227700</v>
       </c>
       <c r="J62" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="K62" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L62" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D63" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E63" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F63">
         <v>2006</v>
@@ -5755,30 +5732,30 @@
         <v>1927300</v>
       </c>
       <c r="J63" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="K63" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="L63" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F64">
         <v>2020</v>
@@ -5793,30 +5770,30 @@
         <v>8183800</v>
       </c>
       <c r="J64" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="K64" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F65">
         <v>2017</v>
@@ -5831,30 +5808,30 @@
         <v>15139200</v>
       </c>
       <c r="J65" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K65" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="L65" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
         <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F66">
         <v>2014</v>
@@ -5869,21 +5846,21 @@
         <v>3225400</v>
       </c>
       <c r="J66" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="K66" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="L66" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B67" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -5892,7 +5869,7 @@
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F67">
         <v>2013</v>
@@ -5907,21 +5884,21 @@
         <v>255000</v>
       </c>
       <c r="J67" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="K67" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L67" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B68" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -5930,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F68">
         <v>2005</v>
@@ -5945,30 +5922,30 @@
         <v>159400</v>
       </c>
       <c r="J68" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="K68" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="L68" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F69">
         <v>2008</v>
@@ -5983,30 +5960,30 @@
         <v>9760800</v>
       </c>
       <c r="J69" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="K69" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="L69" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B70" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E70" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F70">
         <v>2009</v>
@@ -6021,30 +5998,30 @@
         <v>146700</v>
       </c>
       <c r="J70" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="K70" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="L70" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B71" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
         <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F71">
         <v>2017</v>
@@ -6059,30 +6036,30 @@
         <v>3658600</v>
       </c>
       <c r="J71" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="K71" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="L71" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B72" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E72" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F72">
         <v>2010</v>
@@ -6097,30 +6074,30 @@
         <v>1552100</v>
       </c>
       <c r="J72" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="K72" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="L72" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B73" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F73">
         <v>2005</v>
@@ -6135,30 +6112,30 @@
         <v>2988000</v>
       </c>
       <c r="J73" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="K73" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="L73" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" t="s">
         <v>21</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>22</v>
-      </c>
-      <c r="E74" t="s">
-        <v>23</v>
       </c>
       <c r="F74">
         <v>2020</v>
@@ -6173,30 +6150,30 @@
         <v>3104200</v>
       </c>
       <c r="J74" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K74" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="L74" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F75">
         <v>2018</v>
@@ -6211,30 +6188,30 @@
         <v>2360500</v>
       </c>
       <c r="J75" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="K75" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="L75" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B76" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F76">
         <v>2015</v>
@@ -6249,30 +6226,30 @@
         <v>13944000</v>
       </c>
       <c r="J76" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K76" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="L76" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B77" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" t="s">
         <v>21</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>22</v>
-      </c>
-      <c r="E77" t="s">
-        <v>23</v>
       </c>
       <c r="F77">
         <v>2013</v>
@@ -6287,30 +6264,30 @@
         <v>2337300</v>
       </c>
       <c r="J77" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="K77" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="L77" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F78">
         <v>2017</v>
@@ -6325,30 +6302,30 @@
         <v>4541800</v>
       </c>
       <c r="J78" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="K78" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="L78" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B79" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F79">
         <v>2015</v>
@@ -6363,30 +6340,30 @@
         <v>197500</v>
       </c>
       <c r="J79" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="K79" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="L79" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B80" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F80">
         <v>2013</v>
@@ -6401,30 +6378,30 @@
         <v>170000</v>
       </c>
       <c r="J80" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="K80" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="L80" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B81" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F81">
         <v>2017</v>
@@ -6439,30 +6416,30 @@
         <v>201900</v>
       </c>
       <c r="J81" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="K81" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L81" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B82" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F82">
         <v>2021</v>
@@ -6477,30 +6454,30 @@
         <v>6573600</v>
       </c>
       <c r="J82" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K82" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L82" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B83" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F83">
         <v>2007</v>
@@ -6515,30 +6492,30 @@
         <v>4428900</v>
       </c>
       <c r="J83" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="K83" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="L83" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B84" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E84" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F84">
         <v>2014</v>
@@ -6553,30 +6530,30 @@
         <v>6228300</v>
       </c>
       <c r="J84" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="K84" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="L84" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B85" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C85" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F85">
         <v>2023</v>
@@ -6591,30 +6568,30 @@
         <v>5617400</v>
       </c>
       <c r="J85" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="K85" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="L85" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B86" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C86" t="s">
+        <v>20</v>
+      </c>
+      <c r="D86" t="s">
         <v>21</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>22</v>
-      </c>
-      <c r="E86" t="s">
-        <v>23</v>
       </c>
       <c r="F86">
         <v>2024</v>
@@ -6629,30 +6606,30 @@
         <v>3542400</v>
       </c>
       <c r="J86" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="K86" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="L86" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B87" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F87">
         <v>2025</v>
@@ -6667,21 +6644,21 @@
         <v>265600</v>
       </c>
       <c r="J87" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="K87" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="L87" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B88" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6708,18 +6685,18 @@
         <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="L88" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6743,30 +6720,30 @@
         <v>191200</v>
       </c>
       <c r="J89" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="K89" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="L89" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B90" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F90">
         <v>2018</v>
@@ -6781,30 +6758,30 @@
         <v>15736800</v>
       </c>
       <c r="J90" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="K90" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="L90" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E91" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F91">
         <v>2018</v>
@@ -6819,30 +6796,30 @@
         <v>222900</v>
       </c>
       <c r="J91" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="K91" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="L91" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="B92" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F92">
         <v>2010</v>
@@ -6857,30 +6834,30 @@
         <v>3286800</v>
       </c>
       <c r="J92" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="K92" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L92" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B93" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C93" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E93" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F93">
         <v>2017</v>
@@ -6895,30 +6872,30 @@
         <v>2144700</v>
       </c>
       <c r="J93" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="K93" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="L93" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B94" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C94" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E94" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F94">
         <v>2011</v>
@@ -6933,30 +6910,30 @@
         <v>2310700</v>
       </c>
       <c r="J94" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="K94" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="L94" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E95" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F95">
         <v>2009</v>
@@ -6971,30 +6948,30 @@
         <v>276200</v>
       </c>
       <c r="J95" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="K95" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="L95" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B96" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C96" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E96" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F96">
         <v>2010</v>
@@ -7009,30 +6986,30 @@
         <v>2556400</v>
       </c>
       <c r="J96" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K96" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="L96" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B97" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F97">
         <v>2022</v>
@@ -7047,30 +7024,30 @@
         <v>7250900</v>
       </c>
       <c r="J97" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="K97" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="L97" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B98" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E98" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F98">
         <v>2022</v>
@@ -7085,30 +7062,30 @@
         <v>241700</v>
       </c>
       <c r="J98" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="K98" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="L98" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B99" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C99" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F99">
         <v>2005</v>
@@ -7123,30 +7100,30 @@
         <v>1925600</v>
       </c>
       <c r="J99" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="K99" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L99" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B100" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F100">
         <v>2014</v>
@@ -7161,30 +7138,30 @@
         <v>5004900</v>
       </c>
       <c r="J100" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="K100" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="L100" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B101" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D101" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E101" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F101">
         <v>2020</v>
@@ -7199,30 +7176,30 @@
         <v>16932000</v>
       </c>
       <c r="J101" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="K101" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="L101" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B102" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C102" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F102">
         <v>2015</v>
@@ -7237,30 +7214,30 @@
         <v>4183200</v>
       </c>
       <c r="J102" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="K102" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="L102" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B103" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F103">
         <v>2008</v>
@@ -7275,30 +7252,30 @@
         <v>3904300</v>
       </c>
       <c r="J103" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="K103" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="L103" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C104" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F104">
         <v>2012</v>
@@ -7313,30 +7290,30 @@
         <v>1822700</v>
       </c>
       <c r="J104" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="K104" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="L104" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="B105" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E105" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F105">
         <v>2018</v>
@@ -7351,21 +7328,21 @@
         <v>5901300</v>
       </c>
       <c r="J105" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="K105" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="L105" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B106" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -7389,30 +7366,30 @@
         <v>155400</v>
       </c>
       <c r="J106" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="K106" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="L106" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C107" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F107">
         <v>2013</v>
@@ -7427,30 +7404,30 @@
         <v>3081000</v>
       </c>
       <c r="J107" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="K107" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="L107" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B108" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E108" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F108">
         <v>2006</v>
@@ -7465,30 +7442,30 @@
         <v>3212100</v>
       </c>
       <c r="J108" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="K108" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="L108" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C109" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E109" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F109">
         <v>2018</v>
@@ -7503,30 +7480,30 @@
         <v>2360500</v>
       </c>
       <c r="J109" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="K109" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="L109" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D110" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E110" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F110">
         <v>2006</v>
@@ -7541,30 +7518,30 @@
         <v>3997300</v>
       </c>
       <c r="J110" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="K110" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="L110" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B111" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C111" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E111" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F111">
         <v>2018</v>
@@ -7579,30 +7556,30 @@
         <v>3671900</v>
       </c>
       <c r="J111" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="K111" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="L111" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F112">
         <v>2016</v>
@@ -7617,30 +7594,30 @@
         <v>5453100</v>
       </c>
       <c r="J112" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="K112" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="L112" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B113" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F113">
         <v>2007</v>
@@ -7655,21 +7632,21 @@
         <v>2214400</v>
       </c>
       <c r="J113" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="K113" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="L113" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B114" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -7678,7 +7655,7 @@
         <v>15</v>
       </c>
       <c r="E114" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F114">
         <v>2016</v>
@@ -7693,21 +7670,21 @@
         <v>290800</v>
       </c>
       <c r="J114" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="K114" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="L114" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -7731,30 +7708,30 @@
         <v>146400</v>
       </c>
       <c r="J115" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K115" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="L115" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B116" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D116" t="s">
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F116">
         <v>2006</v>
@@ -7769,30 +7746,30 @@
         <v>3426200</v>
       </c>
       <c r="J116" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="K116" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="L116" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B117" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C117" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E117" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F117">
         <v>2007</v>
@@ -7807,30 +7784,30 @@
         <v>2579500</v>
       </c>
       <c r="J117" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="K117" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="L117" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E118" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F118">
         <v>2013</v>
@@ -7845,30 +7822,30 @@
         <v>2974700</v>
       </c>
       <c r="J118" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="K118" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="L118" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B119" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E119" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F119">
         <v>2016</v>
@@ -7883,30 +7860,30 @@
         <v>2060100</v>
       </c>
       <c r="J119" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="K119" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="L119" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B120" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E120" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F120">
         <v>2005</v>
@@ -7921,30 +7898,30 @@
         <v>3851200</v>
       </c>
       <c r="J120" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="K120" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="L120" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B121" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" t="s">
         <v>21</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>22</v>
-      </c>
-      <c r="E121" t="s">
-        <v>23</v>
       </c>
       <c r="F121">
         <v>2008</v>
@@ -7959,21 +7936,21 @@
         <v>1789500</v>
       </c>
       <c r="J121" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="K121" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="L121" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B122" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -7982,7 +7959,7 @@
         <v>15</v>
       </c>
       <c r="E122" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F122">
         <v>2020</v>
@@ -7997,30 +7974,30 @@
         <v>296300</v>
       </c>
       <c r="J122" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="K122" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="L122" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B123" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D123" t="s">
         <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F123">
         <v>2006</v>
@@ -8035,30 +8012,30 @@
         <v>2070000</v>
       </c>
       <c r="J123" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="K123" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="L123" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" t="s">
         <v>21</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>22</v>
-      </c>
-      <c r="E124" t="s">
-        <v>23</v>
       </c>
       <c r="F124">
         <v>2023</v>
@@ -8073,30 +8050,30 @@
         <v>3432900</v>
       </c>
       <c r="J124" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="K124" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="L124" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B125" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C125" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E125" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F125">
         <v>2012</v>
@@ -8111,30 +8088,30 @@
         <v>3037800</v>
       </c>
       <c r="J125" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="K125" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="L125" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B126" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C126" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D126" t="s">
         <v>15</v>
       </c>
       <c r="E126" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F126">
         <v>2015</v>
@@ -8149,30 +8126,30 @@
         <v>2324000</v>
       </c>
       <c r="J126" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="K126" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="L126" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="B127" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="C127" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D127" t="s">
         <v>15</v>
       </c>
       <c r="E127" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F127">
         <v>2023</v>
@@ -8187,30 +8164,30 @@
         <v>7489900</v>
       </c>
       <c r="J127" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="K127" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="L127" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="B128" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C128" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" t="s">
         <v>21</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>22</v>
-      </c>
-      <c r="E128" t="s">
-        <v>23</v>
       </c>
       <c r="F128">
         <v>2013</v>
@@ -8225,30 +8202,30 @@
         <v>2337300</v>
       </c>
       <c r="J128" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="K128" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="L128" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="B129" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E129" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F129">
         <v>2014</v>
@@ -8263,30 +8240,30 @@
         <v>189100</v>
       </c>
       <c r="J129" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="K129" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="L129" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B130" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D130" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E130" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F130">
         <v>2020</v>
@@ -8301,30 +8278,30 @@
         <v>7901600</v>
       </c>
       <c r="J130" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="K130" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="L130" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B131" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" t="s">
         <v>21</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>22</v>
-      </c>
-      <c r="E131" t="s">
-        <v>23</v>
       </c>
       <c r="F131">
         <v>2009</v>
@@ -8339,30 +8316,30 @@
         <v>1899000</v>
       </c>
       <c r="J131" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="K131" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="L131" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B132" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C132" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E132" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F132">
         <v>2019</v>
@@ -8377,21 +8354,21 @@
         <v>3266900</v>
       </c>
       <c r="J132" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K132" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="L132" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B133" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -8415,30 +8392,30 @@
         <v>128500</v>
       </c>
       <c r="J133" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="K133" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="L133" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B134" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C134" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D134" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E134" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F134">
         <v>2020</v>
@@ -8453,30 +8430,30 @@
         <v>3950800</v>
       </c>
       <c r="J134" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="K134" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="L134" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B135" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C135" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E135" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F135">
         <v>2015</v>
@@ -8491,30 +8468,30 @@
         <v>3486000</v>
       </c>
       <c r="J135" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="K135" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="L135" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B136" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C136" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E136" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F136">
         <v>2018</v>
@@ -8529,30 +8506,30 @@
         <v>4429900</v>
       </c>
       <c r="J136" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="K136" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="L136" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B137" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E137" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F137">
         <v>2009</v>
@@ -8567,30 +8544,30 @@
         <v>328000</v>
       </c>
       <c r="J137" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="K137" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="L137" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B138" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="C138" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E138" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F138">
         <v>2018</v>
@@ -8605,30 +8582,30 @@
         <v>4429900</v>
       </c>
       <c r="J138" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="K138" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L138" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B139" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="C139" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E139" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F139">
         <v>2012</v>
@@ -8643,30 +8620,30 @@
         <v>5670600</v>
       </c>
       <c r="J139" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="K139" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="L139" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B140" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C140" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E140" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F140">
         <v>2024</v>
@@ -8681,30 +8658,30 @@
         <v>5439300</v>
       </c>
       <c r="J140" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="K140" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="L140" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="B141" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="C141" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D141" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F141">
         <v>2006</v>
@@ -8719,30 +8696,30 @@
         <v>8565600</v>
       </c>
       <c r="J141" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="K141" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="L141" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B142" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C142" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E142" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F142">
         <v>2025</v>
@@ -8757,30 +8734,30 @@
         <v>4482000</v>
       </c>
       <c r="J142" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="K142" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="L142" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="B143" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F143">
         <v>2006</v>
@@ -8795,30 +8772,30 @@
         <v>4140000</v>
       </c>
       <c r="J143" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K143" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="L143" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B144" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C144" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E144" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F144">
         <v>2025</v>
@@ -8833,30 +8810,30 @@
         <v>4482000</v>
       </c>
       <c r="J144" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="K144" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="L144" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="B145" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D145" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E145" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F145">
         <v>2020</v>
@@ -8871,30 +8848,30 @@
         <v>3950800</v>
       </c>
       <c r="J145" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="K145" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="L145" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="B146" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C146" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D146" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E146" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F146">
         <v>2020</v>
@@ -8909,30 +8886,30 @@
         <v>2680900</v>
       </c>
       <c r="J146" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="K146" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="L146" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B147" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C147" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E147" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F147">
         <v>2018</v>
@@ -8947,21 +8924,21 @@
         <v>2360500</v>
       </c>
       <c r="J147" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="K147" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="L147" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B148" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -8970,7 +8947,7 @@
         <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F148">
         <v>2005</v>
@@ -8985,30 +8962,30 @@
         <v>159400</v>
       </c>
       <c r="J148" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="K148" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="L148" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="B149" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C149" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E149" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F149">
         <v>2025</v>
@@ -9023,30 +9000,30 @@
         <v>2988000</v>
       </c>
       <c r="J149" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="K149" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="L149" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B150" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E150" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F150">
         <v>2025</v>
@@ -9061,30 +9038,30 @@
         <v>7470000</v>
       </c>
       <c r="J150" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="K150" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="L150" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="B151" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="C151" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F151">
         <v>2025</v>
@@ -9099,30 +9076,30 @@
         <v>3320000</v>
       </c>
       <c r="J151" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="K151" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="L151" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="B152" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C152" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D152" t="s">
         <v>15</v>
       </c>
       <c r="E152" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F152">
         <v>2021</v>
@@ -9137,30 +9114,30 @@
         <v>4236300</v>
       </c>
       <c r="J152" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="K152" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="L152" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="B153" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="C153" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E153" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F153">
         <v>2008</v>
@@ -9175,30 +9152,30 @@
         <v>2196200</v>
       </c>
       <c r="J153" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="K153" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="L153" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="B154" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="C154" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D154" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E154" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F154">
         <v>2022</v>
@@ -9213,30 +9190,30 @@
         <v>8459400</v>
       </c>
       <c r="J154" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="K154" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="L154" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="B155" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C155" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D155" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E155" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F155">
         <v>2007</v>
@@ -9251,30 +9228,30 @@
         <v>4276200</v>
       </c>
       <c r="J155" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="K155" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="L155" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="B156" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F156">
         <v>2006</v>
@@ -9289,30 +9266,30 @@
         <v>2070000</v>
       </c>
       <c r="J156" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="K156" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="L156" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="B157" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E157" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F157">
         <v>2018</v>
@@ -9327,30 +9304,30 @@
         <v>419600</v>
       </c>
       <c r="J157" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="K157" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="L157" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="B158" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="C158" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F158">
         <v>2020</v>
@@ -9365,30 +9342,30 @@
         <v>4091900</v>
       </c>
       <c r="J158" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="K158" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="L158" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="B159" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="C159" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E159" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F159">
         <v>2024</v>
@@ -9403,30 +9380,30 @@
         <v>4508600</v>
       </c>
       <c r="J159" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="K159" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="L159" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="B160" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E160" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F160">
         <v>2018</v>
@@ -9441,30 +9418,30 @@
         <v>419600</v>
       </c>
       <c r="J160" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="K160" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="L160" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="B161" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="C161" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D161" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E161" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F161">
         <v>2016</v>
@@ -9479,30 +9456,30 @@
         <v>2908300</v>
       </c>
       <c r="J161" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="K161" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="L161" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="B162" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="C162" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E162" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F162">
         <v>2014</v>
@@ -9517,30 +9494,30 @@
         <v>3225400</v>
       </c>
       <c r="J162" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="K162" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="L162" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="B163" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="C163" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E163" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F163">
         <v>2011</v>
@@ -9555,30 +9532,30 @@
         <v>2792100</v>
       </c>
       <c r="J163" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="K163" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="L163" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="B164" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="C164" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E164" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F164">
         <v>2006</v>
@@ -9593,30 +9570,30 @@
         <v>2569700</v>
       </c>
       <c r="J164" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="K164" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="L164" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="B165" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E165" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F165">
         <v>2018</v>
@@ -9631,30 +9608,30 @@
         <v>498300</v>
       </c>
       <c r="J165" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="K165" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="L165" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="B166" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="C166" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E166" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F166">
         <v>2011</v>
@@ -9669,21 +9646,21 @@
         <v>1733000</v>
       </c>
       <c r="J166" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="K166" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="L166" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="B167" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
@@ -9692,7 +9669,7 @@
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F167">
         <v>2017</v>
@@ -9707,30 +9684,30 @@
         <v>302800</v>
       </c>
       <c r="J167" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="K167" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="L167" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="B168" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="C168" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D168" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E168" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F168">
         <v>2012</v>
@@ -9745,30 +9722,30 @@
         <v>3420600</v>
       </c>
       <c r="J168" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="K168" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="L168" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="B169" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="C169" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E169" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F169">
         <v>2013</v>
@@ -9783,30 +9760,30 @@
         <v>6161900</v>
       </c>
       <c r="J169" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="K169" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="L169" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="B170" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E170" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F170">
         <v>2015</v>
@@ -9821,30 +9798,30 @@
         <v>441600</v>
       </c>
       <c r="J170" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="K170" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="L170" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="B171" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="C171" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D171" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E171" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F171">
         <v>2021</v>
@@ -9859,30 +9836,30 @@
         <v>2483400</v>
       </c>
       <c r="J171" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="K171" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="L171" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="B172" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="C172" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E172" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F172">
         <v>2011</v>
@@ -9897,30 +9874,30 @@
         <v>3252300</v>
       </c>
       <c r="J172" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="K172" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="L172" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="B173" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="C173" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D173" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E173" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F173">
         <v>2012</v>
@@ -9935,21 +9912,21 @@
         <v>2835300</v>
       </c>
       <c r="J173" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="K173" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="L173" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="B174" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
@@ -9973,30 +9950,30 @@
         <v>289800</v>
       </c>
       <c r="J174" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="K174" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="L174" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="B175" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C175" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E175" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F175">
         <v>2025</v>
@@ -10011,30 +9988,30 @@
         <v>7470000</v>
       </c>
       <c r="J175" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="K175" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="L175" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="B176" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C176" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D176" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F176">
         <v>2023</v>
@@ -10049,30 +10026,30 @@
         <v>4525200</v>
       </c>
       <c r="J176" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="K176" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="L176" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="B177" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="C177" t="s">
+        <v>20</v>
+      </c>
+      <c r="D177" t="s">
         <v>21</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>22</v>
-      </c>
-      <c r="E177" t="s">
-        <v>23</v>
       </c>
       <c r="F177">
         <v>2023</v>
@@ -10087,30 +10064,30 @@
         <v>3432900</v>
       </c>
       <c r="J177" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="K177" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="L177" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="B178" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="C178" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D178" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E178" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F178">
         <v>2014</v>
@@ -10125,30 +10102,30 @@
         <v>3757100</v>
       </c>
       <c r="J178" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="K178" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="L178" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="B179" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="C179" t="s">
         <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E179" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F179">
         <v>2011</v>
@@ -10163,30 +10140,30 @@
         <v>308100</v>
       </c>
       <c r="J179" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="K179" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="L179" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="B180" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="C180" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F180">
         <v>2022</v>
@@ -10201,30 +10178,30 @@
         <v>5438200</v>
       </c>
       <c r="J180" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="K180" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="L180" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="B181" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="C181" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E181" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F181">
         <v>2019</v>
@@ -10239,21 +10216,21 @@
         <v>4598200</v>
       </c>
       <c r="J181" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="K181" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="L181" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="B182" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="C182" t="s">
         <v>14</v>
@@ -10262,7 +10239,7 @@
         <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F182">
         <v>2018</v>
@@ -10277,30 +10254,30 @@
         <v>275400</v>
       </c>
       <c r="J182" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="K182" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="L182" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="B183" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C183" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D183" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F183">
         <v>2025</v>
@@ -10315,30 +10292,30 @@
         <v>2988000</v>
       </c>
       <c r="J183" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="K183" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="L183" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="B184" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="C184" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D184" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E184" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F184">
         <v>2018</v>
@@ -10353,30 +10330,30 @@
         <v>2229400</v>
       </c>
       <c r="J184" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="K184" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="L184" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="B185" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="C185" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F185">
         <v>2017</v>
@@ -10391,30 +10368,30 @@
         <v>4541800</v>
       </c>
       <c r="J185" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="K185" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="L185" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="B186" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="C186" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D186" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F186">
         <v>2005</v>
@@ -10429,30 +10406,30 @@
         <v>1925600</v>
       </c>
       <c r="J186" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="K186" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="L186" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="B187" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="C187" t="s">
         <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E187" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F187">
         <v>2008</v>
@@ -10467,30 +10444,30 @@
         <v>130100</v>
       </c>
       <c r="J187" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="K187" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="L187" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="B188" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C188" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D188" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E188" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F188">
         <v>2025</v>
@@ -10505,30 +10482,30 @@
         <v>4648000</v>
       </c>
       <c r="J188" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="K188" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="L188" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="B189" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C189" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D189" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E189" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F189">
         <v>2022</v>
@@ -10543,30 +10520,30 @@
         <v>8459400</v>
       </c>
       <c r="J189" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="K189" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="L189" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="B190" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="C190" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D190" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E190" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F190">
         <v>2016</v>
@@ -10581,30 +10558,30 @@
         <v>14541600</v>
       </c>
       <c r="J190" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="K190" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="L190" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="B191" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="C191" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E191" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F191">
         <v>2008</v>
@@ -10619,30 +10596,30 @@
         <v>2358900</v>
       </c>
       <c r="J191" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="K191" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="L191" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="B192" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="C192" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D192" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E192" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F192">
         <v>2023</v>
@@ -10657,30 +10634,30 @@
         <v>8738200</v>
       </c>
       <c r="J192" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="K192" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="L192" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="B193" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="C193" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E193" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F193">
         <v>2012</v>
@@ -10695,30 +10672,30 @@
         <v>2430200</v>
       </c>
       <c r="J193" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="K193" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="L193" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="B194" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="C194" t="s">
+        <v>20</v>
+      </c>
+      <c r="D194" t="s">
         <v>21</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>22</v>
-      </c>
-      <c r="E194" t="s">
-        <v>23</v>
       </c>
       <c r="F194">
         <v>2019</v>
@@ -10733,30 +10710,30 @@
         <v>2994600</v>
       </c>
       <c r="J194" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="K194" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="L194" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="B195" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
       </c>
       <c r="E195" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F195">
         <v>2019</v>
@@ -10771,30 +10748,30 @@
         <v>6533800</v>
       </c>
       <c r="J195" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="K195" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="L195" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="B196" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C196" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D196" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E196" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F196">
         <v>2006</v>
@@ -10809,30 +10786,30 @@
         <v>8565600</v>
       </c>
       <c r="J196" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="K196" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="L196" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="B197" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="C197" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E197" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F197">
         <v>2018</v>
@@ -10847,30 +10824,30 @@
         <v>2360500</v>
       </c>
       <c r="J197" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="K197" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="L197" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="B198" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="C198" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D198" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E198" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F198">
         <v>2015</v>
@@ -10885,30 +10862,30 @@
         <v>5229000</v>
       </c>
       <c r="J198" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="K198" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="L198" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="B199" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="C199" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D199" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E199" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F199">
         <v>2020</v>
@@ -10923,30 +10900,30 @@
         <v>3950800</v>
       </c>
       <c r="J199" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="K199" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="L199" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="B200" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="C200" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E200" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F200">
         <v>2015</v>
@@ -10961,30 +10938,30 @@
         <v>2091600</v>
       </c>
       <c r="J200" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="K200" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="L200" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="B201" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C201" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D201" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E201" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F201">
         <v>2025</v>
@@ -10999,13 +10976,13 @@
         <v>2988000</v>
       </c>
       <c r="J201" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="K201" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="L201" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
